--- a/data/标签汇总.xlsx
+++ b/data/标签汇总.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="990">
   <si>
     <t>Level 1</t>
   </si>
@@ -3034,10 +3034,26 @@
     <t>经济低迷</t>
   </si>
   <si>
-    <t>夸大失业裁员、经济下行</t>
+    <t>该类标题通过夸大经济下行、失业、裁员、企业倒闭等现状，渲染悲观情绪，制造焦虑与恐慌。常见手段包括：使用绝对化、极端化词汇；缺乏数据支撑的断言；暗示“普遍性”危机；强调个体无力感。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">经济崩盘！大规模裁员潮来了，你准备好了吗？
+楼市断供潮爆发，多少家庭一夜返贫
+失业第180天，我发现这个社会不需要我了
+30岁被裁，35岁没人要，中年人的结局已定
+</t>
   </si>
   <si>
     <t>低俗恶搞</t>
+  </si>
+  <si>
+    <t>该类标题以庸俗、低俗、媚俗为特征，通过性暗示、粗俗语言、身体羞辱、恶趣味、低智搞笑等方式吸引点击。内容常涉及低俗段子、恶搞他人、擦边球、无下限博眼球，缺乏正向价值</t>
+  </si>
+  <si>
+    <t>美女同事喝多了，结果我…（太羞耻了）
+丈母娘半夜敲我门，老婆不在家
+千万别让老婆看到这段视频
+老公不在家，隔壁大哥来“帮忙”</t>
   </si>
 </sst>
 </file>
@@ -3050,7 +3066,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3065,6 +3081,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="16"/>
@@ -3412,7 +3434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3430,6 +3452,39 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -3553,16 +3608,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3571,119 +3623,122 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3708,10 +3763,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4248,21 +4321,21 @@
   <dimension ref="A1:E455"/>
   <sheetFormatPr defaultColWidth="8.72566371681416" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="12.7256637168142" style="8" customWidth="1"/>
-    <col min="2" max="2" width="14.7256637168142" style="8" customWidth="1"/>
-    <col min="3" max="3" width="29.0884955752212" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.7256637168142" style="14" customWidth="1"/>
+    <col min="2" max="2" width="14.7256637168142" style="14" customWidth="1"/>
+    <col min="3" max="3" width="29.0884955752212" style="14" customWidth="1"/>
     <col min="4" max="4" width="32.6371681415929" customWidth="1"/>
     <col min="5" max="6" width="20.6371681415929" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="14" customHeight="1" spans="1:5">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -4273,13 +4346,13 @@
       </c>
     </row>
     <row r="2" ht="14" customHeight="1" spans="1:5">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="14" t="s">
         <v>7</v>
       </c>
       <c r="D2" t="s">
@@ -4287,13 +4360,13 @@
       </c>
     </row>
     <row r="3" ht="14" customHeight="1" spans="1:5">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="14" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
@@ -4301,13 +4374,13 @@
       </c>
     </row>
     <row r="4" ht="14" customHeight="1" spans="1:5">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="14" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
@@ -4315,13 +4388,13 @@
       </c>
     </row>
     <row r="5" ht="14" customHeight="1" spans="1:5">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
@@ -4329,13 +4402,13 @@
       </c>
     </row>
     <row r="6" ht="14" customHeight="1" spans="1:5">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="14" t="s">
         <v>15</v>
       </c>
       <c r="D6" t="s">
@@ -4343,13 +4416,13 @@
       </c>
     </row>
     <row r="7" ht="14" customHeight="1" spans="1:5">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
@@ -4357,13 +4430,13 @@
       </c>
     </row>
     <row r="8" ht="14" customHeight="1" spans="1:5">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="14" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
@@ -4371,13 +4444,13 @@
       </c>
     </row>
     <row r="9" ht="14" customHeight="1" spans="1:5">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
       <c r="D9" t="s">
@@ -4385,13 +4458,13 @@
       </c>
     </row>
     <row r="10" ht="14" customHeight="1" spans="1:5">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="14" t="s">
         <v>24</v>
       </c>
       <c r="D10" t="s">
@@ -4399,13 +4472,13 @@
       </c>
     </row>
     <row r="11" ht="14" customHeight="1" spans="1:5">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="14" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
@@ -4413,13 +4486,13 @@
       </c>
     </row>
     <row r="12" ht="14" customHeight="1" spans="1:5">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="14" t="s">
         <v>29</v>
       </c>
       <c r="D12" t="s">
@@ -4427,13 +4500,13 @@
       </c>
     </row>
     <row r="13" ht="14" customHeight="1" spans="1:5">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="D13" t="s">
@@ -4441,13 +4514,13 @@
       </c>
     </row>
     <row r="14" ht="14" customHeight="1" spans="1:5">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="14" t="s">
         <v>33</v>
       </c>
       <c r="D14" t="s">
@@ -4455,13 +4528,13 @@
       </c>
     </row>
     <row r="15" ht="14" customHeight="1" spans="1:5">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="14" t="s">
         <v>35</v>
       </c>
       <c r="D15" t="s">
@@ -4469,13 +4542,13 @@
       </c>
     </row>
     <row r="16" ht="14" customHeight="1" spans="1:5">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="14" t="s">
         <v>37</v>
       </c>
       <c r="D16" t="s">
@@ -4483,13 +4556,13 @@
       </c>
     </row>
     <row r="17" ht="14" customHeight="1" spans="1:4">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="14" t="s">
         <v>40</v>
       </c>
       <c r="D17" t="s">
@@ -4497,13 +4570,13 @@
       </c>
     </row>
     <row r="18" ht="14" customHeight="1" spans="1:4">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="14" t="s">
         <v>42</v>
       </c>
       <c r="D18" t="s">
@@ -4511,13 +4584,13 @@
       </c>
     </row>
     <row r="19" ht="14" customHeight="1" spans="1:4">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="14" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
@@ -4525,13 +4598,13 @@
       </c>
     </row>
     <row r="20" ht="14" customHeight="1" spans="1:4">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="14" t="s">
         <v>46</v>
       </c>
       <c r="D20" t="s">
@@ -4539,13 +4612,13 @@
       </c>
     </row>
     <row r="21" ht="14" customHeight="1" spans="1:4">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="14" t="s">
         <v>48</v>
       </c>
       <c r="D21" t="s">
@@ -4553,13 +4626,13 @@
       </c>
     </row>
     <row r="22" ht="14" customHeight="1" spans="1:4">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="14" t="s">
         <v>51</v>
       </c>
       <c r="D22" t="s">
@@ -4567,13 +4640,13 @@
       </c>
     </row>
     <row r="23" ht="14" customHeight="1" spans="1:4">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="14" t="s">
         <v>53</v>
       </c>
       <c r="D23" t="s">
@@ -4581,13 +4654,13 @@
       </c>
     </row>
     <row r="24" ht="14" customHeight="1" spans="1:4">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="14" t="s">
         <v>55</v>
       </c>
       <c r="D24" t="s">
@@ -4595,13 +4668,13 @@
       </c>
     </row>
     <row r="25" ht="14" customHeight="1" spans="1:4">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C25" s="14" t="s">
         <v>57</v>
       </c>
       <c r="D25" t="s">
@@ -4609,13 +4682,13 @@
       </c>
     </row>
     <row r="26" ht="14" customHeight="1" spans="1:4">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="C26" s="14" t="s">
         <v>59</v>
       </c>
       <c r="D26" t="s">
@@ -4623,13 +4696,13 @@
       </c>
     </row>
     <row r="27" ht="14" customHeight="1" spans="1:4">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="C27" s="14" t="s">
         <v>62</v>
       </c>
       <c r="D27" t="s">
@@ -4637,13 +4710,13 @@
       </c>
     </row>
     <row r="28" ht="14" customHeight="1" spans="1:4">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="14" t="s">
         <v>64</v>
       </c>
       <c r="D28" t="s">
@@ -4651,13 +4724,13 @@
       </c>
     </row>
     <row r="29" ht="14" customHeight="1" spans="1:4">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="14" t="s">
         <v>66</v>
       </c>
       <c r="D29" t="s">
@@ -4665,13 +4738,13 @@
       </c>
     </row>
     <row r="30" ht="14" customHeight="1" spans="1:4">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="8" t="s">
+      <c r="C30" s="14" t="s">
         <v>68</v>
       </c>
       <c r="D30" t="s">
@@ -4679,13 +4752,13 @@
       </c>
     </row>
     <row r="31" ht="14" customHeight="1" spans="1:4">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="8" t="s">
+      <c r="C31" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D31" t="s">
@@ -4693,13 +4766,13 @@
       </c>
     </row>
     <row r="32" ht="14" customHeight="1" spans="1:4">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="8" t="s">
+      <c r="C32" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D32" t="s">
@@ -4707,13 +4780,13 @@
       </c>
     </row>
     <row r="33" ht="14" customHeight="1" spans="1:4">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C33" s="8" t="s">
+      <c r="C33" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D33" t="s">
@@ -4721,13 +4794,13 @@
       </c>
     </row>
     <row r="34" ht="14" customHeight="1" spans="1:4">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="14" t="s">
         <v>78</v>
       </c>
       <c r="D34" t="s">
@@ -4735,13 +4808,13 @@
       </c>
     </row>
     <row r="35" ht="14" customHeight="1" spans="1:4">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="14" t="s">
         <v>80</v>
       </c>
       <c r="D35" t="s">
@@ -4749,13 +4822,13 @@
       </c>
     </row>
     <row r="36" ht="14" customHeight="1" spans="1:4">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="C36" s="8" t="s">
+      <c r="C36" s="14" t="s">
         <v>82</v>
       </c>
       <c r="D36" t="s">
@@ -4763,13 +4836,13 @@
       </c>
     </row>
     <row r="37" ht="14" customHeight="1" spans="1:4">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C37" s="8" t="s">
+      <c r="C37" s="14" t="s">
         <v>85</v>
       </c>
       <c r="D37" t="s">
@@ -4777,13 +4850,13 @@
       </c>
     </row>
     <row r="38" ht="14" customHeight="1" spans="1:4">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="8" t="s">
+      <c r="C38" s="14" t="s">
         <v>87</v>
       </c>
       <c r="D38" t="s">
@@ -4791,13 +4864,13 @@
       </c>
     </row>
     <row r="39" ht="14" customHeight="1" spans="1:4">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C39" s="8" t="s">
+      <c r="C39" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D39" t="s">
@@ -4805,13 +4878,13 @@
       </c>
     </row>
     <row r="40" ht="14" customHeight="1" spans="1:4">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="8" t="s">
+      <c r="C40" s="14" t="s">
         <v>91</v>
       </c>
       <c r="D40" t="s">
@@ -4819,13 +4892,13 @@
       </c>
     </row>
     <row r="41" ht="14" customHeight="1" spans="1:4">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="8" t="s">
+      <c r="C41" s="14" t="s">
         <v>93</v>
       </c>
       <c r="D41" t="s">
@@ -4833,13 +4906,13 @@
       </c>
     </row>
     <row r="42" ht="14" customHeight="1" spans="1:4">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="14" t="s">
         <v>96</v>
       </c>
       <c r="D42" t="s">
@@ -4847,13 +4920,13 @@
       </c>
     </row>
     <row r="43" ht="14" customHeight="1" spans="1:4">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C43" s="8" t="s">
+      <c r="C43" s="14" t="s">
         <v>98</v>
       </c>
       <c r="D43" t="s">
@@ -4861,13 +4934,13 @@
       </c>
     </row>
     <row r="44" ht="14" customHeight="1" spans="1:4">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="8" t="s">
+      <c r="C44" s="14" t="s">
         <v>100</v>
       </c>
       <c r="D44" t="s">
@@ -4875,13 +4948,13 @@
       </c>
     </row>
     <row r="45" ht="14" customHeight="1" spans="1:4">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="8" t="s">
+      <c r="C45" s="14" t="s">
         <v>102</v>
       </c>
       <c r="D45" t="s">
@@ -4889,13 +4962,13 @@
       </c>
     </row>
     <row r="46" ht="14" customHeight="1" spans="1:4">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C46" s="8" t="s">
+      <c r="C46" s="14" t="s">
         <v>104</v>
       </c>
       <c r="D46" t="s">
@@ -4903,13 +4976,13 @@
       </c>
     </row>
     <row r="47" ht="14" customHeight="1" spans="1:4">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="8" t="s">
+      <c r="C47" s="14" t="s">
         <v>107</v>
       </c>
       <c r="D47" t="s">
@@ -4917,13 +4990,13 @@
       </c>
     </row>
     <row r="48" ht="14" customHeight="1" spans="1:4">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="14" t="s">
         <v>109</v>
       </c>
       <c r="D48" t="s">
@@ -4931,13 +5004,13 @@
       </c>
     </row>
     <row r="49" ht="14" customHeight="1" spans="1:4">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="14" t="s">
         <v>111</v>
       </c>
       <c r="D49" t="s">
@@ -4945,13 +5018,13 @@
       </c>
     </row>
     <row r="50" ht="14" customHeight="1" spans="1:4">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C50" s="8" t="s">
+      <c r="C50" s="14" t="s">
         <v>113</v>
       </c>
       <c r="D50" t="s">
@@ -4959,13 +5032,13 @@
       </c>
     </row>
     <row r="51" ht="14" customHeight="1" spans="1:4">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="C51" s="8" t="s">
+      <c r="C51" s="14" t="s">
         <v>115</v>
       </c>
       <c r="D51" t="s">
@@ -4973,13 +5046,13 @@
       </c>
     </row>
     <row r="52" ht="14" customHeight="1" spans="1:4">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C52" s="8" t="s">
+      <c r="C52" s="14" t="s">
         <v>118</v>
       </c>
       <c r="D52" t="s">
@@ -4987,13 +5060,13 @@
       </c>
     </row>
     <row r="53" ht="14" customHeight="1" spans="1:4">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C53" s="8" t="s">
+      <c r="C53" s="14" t="s">
         <v>120</v>
       </c>
       <c r="D53" t="s">
@@ -5001,13 +5074,13 @@
       </c>
     </row>
     <row r="54" ht="14" customHeight="1" spans="1:4">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="8" t="s">
+      <c r="C54" s="14" t="s">
         <v>122</v>
       </c>
       <c r="D54" t="s">
@@ -5015,13 +5088,13 @@
       </c>
     </row>
     <row r="55" ht="14" customHeight="1" spans="1:4">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C55" s="8" t="s">
+      <c r="C55" s="14" t="s">
         <v>124</v>
       </c>
       <c r="D55" t="s">
@@ -5029,13 +5102,13 @@
       </c>
     </row>
     <row r="56" ht="14" customHeight="1" spans="1:4">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C56" s="14" t="s">
         <v>126</v>
       </c>
       <c r="D56" t="s">
@@ -5043,13 +5116,13 @@
       </c>
     </row>
     <row r="57" ht="14" customHeight="1" spans="1:4">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C57" s="14" t="s">
         <v>129</v>
       </c>
       <c r="D57" t="s">
@@ -5057,13 +5130,13 @@
       </c>
     </row>
     <row r="58" ht="14" customHeight="1" spans="1:4">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="8" t="s">
+      <c r="C58" s="14" t="s">
         <v>131</v>
       </c>
       <c r="D58" t="s">
@@ -5071,13 +5144,13 @@
       </c>
     </row>
     <row r="59" ht="14" customHeight="1" spans="1:4">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="14" t="s">
         <v>133</v>
       </c>
       <c r="D59" t="s">
@@ -5085,13 +5158,13 @@
       </c>
     </row>
     <row r="60" ht="14" customHeight="1" spans="1:4">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="14" t="s">
         <v>135</v>
       </c>
       <c r="D60" t="s">
@@ -5099,13 +5172,13 @@
       </c>
     </row>
     <row r="61" ht="14" customHeight="1" spans="1:4">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="14" t="s">
         <v>139</v>
       </c>
       <c r="D61" t="s">
@@ -5113,13 +5186,13 @@
       </c>
     </row>
     <row r="62" ht="14" customHeight="1" spans="1:4">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C62" s="8" t="s">
+      <c r="C62" s="14" t="s">
         <v>141</v>
       </c>
       <c r="D62" t="s">
@@ -5127,13 +5200,13 @@
       </c>
     </row>
     <row r="63" ht="14" customHeight="1" spans="1:4">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C63" s="8" t="s">
+      <c r="C63" s="14" t="s">
         <v>143</v>
       </c>
       <c r="D63" t="s">
@@ -5141,13 +5214,13 @@
       </c>
     </row>
     <row r="64" ht="14" customHeight="1" spans="1:4">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C64" s="8" t="s">
+      <c r="C64" s="14" t="s">
         <v>145</v>
       </c>
       <c r="D64" t="s">
@@ -5155,13 +5228,13 @@
       </c>
     </row>
     <row r="65" ht="14" customHeight="1" spans="1:4">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="8" t="s">
+      <c r="C65" s="14" t="s">
         <v>147</v>
       </c>
       <c r="D65" t="s">
@@ -5169,13 +5242,13 @@
       </c>
     </row>
     <row r="66" ht="14" customHeight="1" spans="1:4">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C66" s="14" t="s">
         <v>150</v>
       </c>
       <c r="D66" t="s">
@@ -5183,13 +5256,13 @@
       </c>
     </row>
     <row r="67" ht="14" customHeight="1" spans="1:4">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C67" s="14" t="s">
         <v>152</v>
       </c>
       <c r="D67" t="s">
@@ -5197,13 +5270,13 @@
       </c>
     </row>
     <row r="68" ht="14" customHeight="1" spans="1:4">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C68" s="8" t="s">
+      <c r="C68" s="14" t="s">
         <v>154</v>
       </c>
       <c r="D68" t="s">
@@ -5211,13 +5284,13 @@
       </c>
     </row>
     <row r="69" ht="14" customHeight="1" spans="1:4">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C69" s="14" t="s">
         <v>156</v>
       </c>
       <c r="D69" t="s">
@@ -5225,13 +5298,13 @@
       </c>
     </row>
     <row r="70" ht="14" customHeight="1" spans="1:4">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="C70" s="8" t="s">
+      <c r="C70" s="14" t="s">
         <v>158</v>
       </c>
       <c r="D70" t="s">
@@ -5239,13 +5312,13 @@
       </c>
     </row>
     <row r="71" ht="14" customHeight="1" spans="1:4">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C71" s="14" t="s">
         <v>161</v>
       </c>
       <c r="D71" t="s">
@@ -5253,13 +5326,13 @@
       </c>
     </row>
     <row r="72" ht="14" customHeight="1" spans="1:4">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="8" t="s">
+      <c r="C72" s="14" t="s">
         <v>163</v>
       </c>
       <c r="D72" t="s">
@@ -5267,13 +5340,13 @@
       </c>
     </row>
     <row r="73" ht="14" customHeight="1" spans="1:4">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C73" s="8" t="s">
+      <c r="C73" s="14" t="s">
         <v>165</v>
       </c>
       <c r="D73" t="s">
@@ -5281,13 +5354,13 @@
       </c>
     </row>
     <row r="74" ht="14" customHeight="1" spans="1:4">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="14" t="s">
         <v>167</v>
       </c>
       <c r="D74" t="s">
@@ -5295,13 +5368,13 @@
       </c>
     </row>
     <row r="75" ht="14" customHeight="1" spans="1:4">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="14" t="s">
         <v>169</v>
       </c>
       <c r="D75" t="s">
@@ -5309,13 +5382,13 @@
       </c>
     </row>
     <row r="76" ht="14" customHeight="1" spans="1:4">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="8" t="s">
+      <c r="C76" s="14" t="s">
         <v>172</v>
       </c>
       <c r="D76" t="s">
@@ -5323,13 +5396,13 @@
       </c>
     </row>
     <row r="77" ht="14" customHeight="1" spans="1:4">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C77" s="8" t="s">
+      <c r="C77" s="14" t="s">
         <v>174</v>
       </c>
       <c r="D77" t="s">
@@ -5337,13 +5410,13 @@
       </c>
     </row>
     <row r="78" ht="14" customHeight="1" spans="1:4">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C78" s="8" t="s">
+      <c r="C78" s="14" t="s">
         <v>176</v>
       </c>
       <c r="D78" t="s">
@@ -5351,13 +5424,13 @@
       </c>
     </row>
     <row r="79" ht="14" customHeight="1" spans="1:4">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C79" s="14" t="s">
         <v>178</v>
       </c>
       <c r="D79" t="s">
@@ -5365,13 +5438,13 @@
       </c>
     </row>
     <row r="80" ht="14" customHeight="1" spans="1:4">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="14" t="s">
         <v>180</v>
       </c>
       <c r="D80" t="s">
@@ -5379,13 +5452,13 @@
       </c>
     </row>
     <row r="81" ht="14" customHeight="1" spans="1:4">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="14" t="s">
         <v>183</v>
       </c>
       <c r="D81" t="s">
@@ -5393,13 +5466,13 @@
       </c>
     </row>
     <row r="82" ht="14" customHeight="1" spans="1:4">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C82" s="14" t="s">
         <v>185</v>
       </c>
       <c r="D82" t="s">
@@ -5407,13 +5480,13 @@
       </c>
     </row>
     <row r="83" ht="14" customHeight="1" spans="1:4">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="14" t="s">
         <v>187</v>
       </c>
       <c r="D83" t="s">
@@ -5421,13 +5494,13 @@
       </c>
     </row>
     <row r="84" ht="14" customHeight="1" spans="1:4">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="14" t="s">
         <v>189</v>
       </c>
       <c r="D84" t="s">
@@ -5435,13 +5508,13 @@
       </c>
     </row>
     <row r="85" ht="14" customHeight="1" spans="1:4">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="C85" s="8" t="s">
+      <c r="C85" s="14" t="s">
         <v>191</v>
       </c>
       <c r="D85" t="s">
@@ -5449,13 +5522,13 @@
       </c>
     </row>
     <row r="86" ht="14" customHeight="1" spans="1:4">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="8" t="s">
+      <c r="C86" s="14" t="s">
         <v>194</v>
       </c>
       <c r="D86" t="s">
@@ -5463,13 +5536,13 @@
       </c>
     </row>
     <row r="87" ht="14" customHeight="1" spans="1:4">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C87" s="8" t="s">
+      <c r="C87" s="14" t="s">
         <v>196</v>
       </c>
       <c r="D87" t="s">
@@ -5477,13 +5550,13 @@
       </c>
     </row>
     <row r="88" ht="14" customHeight="1" spans="1:4">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C88" s="8" t="s">
+      <c r="C88" s="14" t="s">
         <v>198</v>
       </c>
       <c r="D88" t="s">
@@ -5491,13 +5564,13 @@
       </c>
     </row>
     <row r="89" ht="14" customHeight="1" spans="1:4">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C89" s="8" t="s">
+      <c r="C89" s="14" t="s">
         <v>200</v>
       </c>
       <c r="D89" t="s">
@@ -5505,13 +5578,13 @@
       </c>
     </row>
     <row r="90" ht="14" customHeight="1" spans="1:4">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="14" t="s">
         <v>202</v>
       </c>
       <c r="D90" t="s">
@@ -5519,13 +5592,13 @@
       </c>
     </row>
     <row r="91" ht="14" customHeight="1" spans="1:4">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="14" t="s">
         <v>205</v>
       </c>
       <c r="D91" t="s">
@@ -5533,13 +5606,13 @@
       </c>
     </row>
     <row r="92" ht="14" customHeight="1" spans="1:4">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="14" t="s">
         <v>207</v>
       </c>
       <c r="D92" t="s">
@@ -5547,13 +5620,13 @@
       </c>
     </row>
     <row r="93" ht="14" customHeight="1" spans="1:4">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="14" t="s">
         <v>209</v>
       </c>
       <c r="D93" t="s">
@@ -5561,13 +5634,13 @@
       </c>
     </row>
     <row r="94" ht="14" customHeight="1" spans="1:4">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="14" t="s">
         <v>211</v>
       </c>
       <c r="D94" t="s">
@@ -5575,13 +5648,13 @@
       </c>
     </row>
     <row r="95" ht="14" customHeight="1" spans="1:4">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="14" t="s">
         <v>213</v>
       </c>
       <c r="D95" t="s">
@@ -5589,13 +5662,13 @@
       </c>
     </row>
     <row r="96" ht="14" customHeight="1" spans="1:4">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="14" t="s">
         <v>216</v>
       </c>
       <c r="D96" t="s">
@@ -5603,13 +5676,13 @@
       </c>
     </row>
     <row r="97" ht="14" customHeight="1" spans="1:4">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="14" t="s">
         <v>218</v>
       </c>
       <c r="D97" t="s">
@@ -5617,13 +5690,13 @@
       </c>
     </row>
     <row r="98" ht="14" customHeight="1" spans="1:4">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="14" t="s">
         <v>220</v>
       </c>
       <c r="D98" t="s">
@@ -5631,13 +5704,13 @@
       </c>
     </row>
     <row r="99" ht="14" customHeight="1" spans="1:4">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="14" t="s">
         <v>222</v>
       </c>
       <c r="D99" t="s">
@@ -5645,13 +5718,13 @@
       </c>
     </row>
     <row r="100" ht="14" customHeight="1" spans="1:4">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="14" t="s">
         <v>224</v>
       </c>
       <c r="D100" t="s">
@@ -5659,13 +5732,13 @@
       </c>
     </row>
     <row r="101" ht="14" customHeight="1" spans="1:4">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="14" t="s">
         <v>228</v>
       </c>
       <c r="D101" t="s">
@@ -5673,13 +5746,13 @@
       </c>
     </row>
     <row r="102" ht="14" customHeight="1" spans="1:4">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C102" s="14" t="s">
         <v>230</v>
       </c>
       <c r="D102" t="s">
@@ -5687,13 +5760,13 @@
       </c>
     </row>
     <row r="103" ht="14" customHeight="1" spans="1:4">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C103" s="8" t="s">
+      <c r="C103" s="14" t="s">
         <v>232</v>
       </c>
       <c r="D103" t="s">
@@ -5701,13 +5774,13 @@
       </c>
     </row>
     <row r="104" ht="14" customHeight="1" spans="1:4">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C104" s="14" t="s">
         <v>234</v>
       </c>
       <c r="D104" t="s">
@@ -5715,13 +5788,13 @@
       </c>
     </row>
     <row r="105" ht="14" customHeight="1" spans="1:4">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="8" t="s">
+      <c r="C105" s="14" t="s">
         <v>236</v>
       </c>
       <c r="D105" t="s">
@@ -5729,13 +5802,13 @@
       </c>
     </row>
     <row r="106" ht="14" customHeight="1" spans="1:4">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C106" s="8" t="s">
+      <c r="C106" s="14" t="s">
         <v>239</v>
       </c>
       <c r="D106" t="s">
@@ -5743,13 +5816,13 @@
       </c>
     </row>
     <row r="107" ht="14" customHeight="1" spans="1:4">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="C107" s="14" t="s">
         <v>241</v>
       </c>
       <c r="D107" t="s">
@@ -5757,13 +5830,13 @@
       </c>
     </row>
     <row r="108" ht="14" customHeight="1" spans="1:4">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="C108" s="14" t="s">
         <v>243</v>
       </c>
       <c r="D108" t="s">
@@ -5771,13 +5844,13 @@
       </c>
     </row>
     <row r="109" ht="14" customHeight="1" spans="1:4">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C109" s="8" t="s">
+      <c r="C109" s="14" t="s">
         <v>245</v>
       </c>
       <c r="D109" t="s">
@@ -5785,13 +5858,13 @@
       </c>
     </row>
     <row r="110" ht="14" customHeight="1" spans="1:4">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="B110" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C110" s="8" t="s">
+      <c r="C110" s="14" t="s">
         <v>247</v>
       </c>
       <c r="D110" t="s">
@@ -5799,13 +5872,13 @@
       </c>
     </row>
     <row r="111" ht="14" customHeight="1" spans="1:4">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C111" s="8" t="s">
+      <c r="C111" s="14" t="s">
         <v>250</v>
       </c>
       <c r="D111" t="s">
@@ -5813,13 +5886,13 @@
       </c>
     </row>
     <row r="112" ht="14" customHeight="1" spans="1:4">
-      <c r="A112" s="8" t="s">
+      <c r="A112" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="14" t="s">
         <v>252</v>
       </c>
       <c r="D112" t="s">
@@ -5827,13 +5900,13 @@
       </c>
     </row>
     <row r="113" ht="14" customHeight="1" spans="1:4">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C113" s="8" t="s">
+      <c r="C113" s="14" t="s">
         <v>254</v>
       </c>
       <c r="D113" t="s">
@@ -5841,13 +5914,13 @@
       </c>
     </row>
     <row r="114" ht="14" customHeight="1" spans="1:4">
-      <c r="A114" s="8" t="s">
+      <c r="A114" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="B114" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C114" s="8" t="s">
+      <c r="C114" s="14" t="s">
         <v>256</v>
       </c>
       <c r="D114" t="s">
@@ -5855,13 +5928,13 @@
       </c>
     </row>
     <row r="115" ht="14" customHeight="1" spans="1:4">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="B115" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C115" s="8" t="s">
+      <c r="C115" s="14" t="s">
         <v>258</v>
       </c>
       <c r="D115" t="s">
@@ -5869,13 +5942,13 @@
       </c>
     </row>
     <row r="116" ht="14" customHeight="1" spans="1:4">
-      <c r="A116" s="8" t="s">
+      <c r="A116" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C116" s="8" t="s">
+      <c r="C116" s="14" t="s">
         <v>261</v>
       </c>
       <c r="D116" t="s">
@@ -5883,13 +5956,13 @@
       </c>
     </row>
     <row r="117" ht="14" customHeight="1" spans="1:4">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C117" s="8" t="s">
+      <c r="C117" s="14" t="s">
         <v>263</v>
       </c>
       <c r="D117" t="s">
@@ -5897,13 +5970,13 @@
       </c>
     </row>
     <row r="118" ht="14" customHeight="1" spans="1:4">
-      <c r="A118" s="8" t="s">
+      <c r="A118" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C118" s="8" t="s">
+      <c r="C118" s="14" t="s">
         <v>265</v>
       </c>
       <c r="D118" t="s">
@@ -5911,13 +5984,13 @@
       </c>
     </row>
     <row r="119" ht="14" customHeight="1" spans="1:4">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C119" s="8" t="s">
+      <c r="C119" s="14" t="s">
         <v>267</v>
       </c>
       <c r="D119" t="s">
@@ -5925,13 +5998,13 @@
       </c>
     </row>
     <row r="120" ht="14" customHeight="1" spans="1:4">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C120" s="8" t="s">
+      <c r="C120" s="14" t="s">
         <v>269</v>
       </c>
       <c r="D120" t="s">
@@ -5939,13 +6012,13 @@
       </c>
     </row>
     <row r="121" ht="14" customHeight="1" spans="1:4">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B121" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C121" s="8" t="s">
+      <c r="C121" s="14" t="s">
         <v>272</v>
       </c>
       <c r="D121" t="s">
@@ -5953,13 +6026,13 @@
       </c>
     </row>
     <row r="122" ht="14" customHeight="1" spans="1:4">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C122" s="8" t="s">
+      <c r="C122" s="14" t="s">
         <v>274</v>
       </c>
       <c r="D122" t="s">
@@ -5967,13 +6040,13 @@
       </c>
     </row>
     <row r="123" ht="14" customHeight="1" spans="1:4">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B123" s="8" t="s">
+      <c r="B123" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C123" s="8" t="s">
+      <c r="C123" s="14" t="s">
         <v>276</v>
       </c>
       <c r="D123" t="s">
@@ -5981,13 +6054,13 @@
       </c>
     </row>
     <row r="124" ht="14" customHeight="1" spans="1:4">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C124" s="8" t="s">
+      <c r="C124" s="14" t="s">
         <v>278</v>
       </c>
       <c r="D124" t="s">
@@ -5995,13 +6068,13 @@
       </c>
     </row>
     <row r="125" ht="14" customHeight="1" spans="1:4">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="C125" s="8" t="s">
+      <c r="C125" s="14" t="s">
         <v>280</v>
       </c>
       <c r="D125" t="s">
@@ -6009,13 +6082,13 @@
       </c>
     </row>
     <row r="126" ht="14" customHeight="1" spans="1:4">
-      <c r="A126" s="8" t="s">
+      <c r="A126" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C126" s="8" t="s">
+      <c r="C126" s="14" t="s">
         <v>283</v>
       </c>
       <c r="D126" t="s">
@@ -6023,13 +6096,13 @@
       </c>
     </row>
     <row r="127" ht="14" customHeight="1" spans="1:4">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C127" s="8" t="s">
+      <c r="C127" s="14" t="s">
         <v>285</v>
       </c>
       <c r="D127" t="s">
@@ -6037,13 +6110,13 @@
       </c>
     </row>
     <row r="128" ht="14" customHeight="1" spans="1:4">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C128" s="8" t="s">
+      <c r="C128" s="14" t="s">
         <v>287</v>
       </c>
       <c r="D128" t="s">
@@ -6051,13 +6124,13 @@
       </c>
     </row>
     <row r="129" ht="14" customHeight="1" spans="1:4">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C129" s="8" t="s">
+      <c r="C129" s="14" t="s">
         <v>289</v>
       </c>
       <c r="D129" t="s">
@@ -6065,13 +6138,13 @@
       </c>
     </row>
     <row r="130" ht="14" customHeight="1" spans="1:4">
-      <c r="A130" s="8" t="s">
+      <c r="A130" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C130" s="8" t="s">
+      <c r="C130" s="14" t="s">
         <v>291</v>
       </c>
       <c r="D130" t="s">
@@ -6079,13 +6152,13 @@
       </c>
     </row>
     <row r="131" ht="14" customHeight="1" spans="1:4">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="C131" s="8" t="s">
+      <c r="C131" s="14" t="s">
         <v>293</v>
       </c>
       <c r="D131" t="s">
@@ -6093,13 +6166,13 @@
       </c>
     </row>
     <row r="132" ht="14" customHeight="1" spans="1:4">
-      <c r="A132" s="8" t="s">
+      <c r="A132" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C132" s="8" t="s">
+      <c r="C132" s="14" t="s">
         <v>297</v>
       </c>
       <c r="D132" t="s">
@@ -6107,13 +6180,13 @@
       </c>
     </row>
     <row r="133" ht="14" customHeight="1" spans="1:4">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C133" s="8" t="s">
+      <c r="C133" s="14" t="s">
         <v>299</v>
       </c>
       <c r="D133" t="s">
@@ -6121,13 +6194,13 @@
       </c>
     </row>
     <row r="134" ht="14" customHeight="1" spans="1:4">
-      <c r="A134" s="8" t="s">
+      <c r="A134" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C134" s="8" t="s">
+      <c r="C134" s="14" t="s">
         <v>301</v>
       </c>
       <c r="D134" t="s">
@@ -6135,13 +6208,13 @@
       </c>
     </row>
     <row r="135" ht="14" customHeight="1" spans="1:4">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C135" s="8" t="s">
+      <c r="C135" s="14" t="s">
         <v>303</v>
       </c>
       <c r="D135" t="s">
@@ -6149,13 +6222,13 @@
       </c>
     </row>
     <row r="136" ht="14" customHeight="1" spans="1:4">
-      <c r="A136" s="8" t="s">
+      <c r="A136" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B136" s="8" t="s">
+      <c r="B136" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C136" s="8" t="s">
+      <c r="C136" s="14" t="s">
         <v>305</v>
       </c>
       <c r="D136" t="s">
@@ -6163,13 +6236,13 @@
       </c>
     </row>
     <row r="137" ht="14" customHeight="1" spans="1:4">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="B137" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C137" s="8" t="s">
+      <c r="C137" s="14" t="s">
         <v>308</v>
       </c>
       <c r="D137" t="s">
@@ -6177,13 +6250,13 @@
       </c>
     </row>
     <row r="138" ht="14" customHeight="1" spans="1:4">
-      <c r="A138" s="8" t="s">
+      <c r="A138" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C138" s="8" t="s">
+      <c r="C138" s="14" t="s">
         <v>310</v>
       </c>
       <c r="D138" t="s">
@@ -6191,13 +6264,13 @@
       </c>
     </row>
     <row r="139" ht="14" customHeight="1" spans="1:4">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="B139" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C139" s="8" t="s">
+      <c r="C139" s="14" t="s">
         <v>312</v>
       </c>
       <c r="D139" t="s">
@@ -6205,13 +6278,13 @@
       </c>
     </row>
     <row r="140" ht="14" customHeight="1" spans="1:4">
-      <c r="A140" s="8" t="s">
+      <c r="A140" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="B140" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="C140" s="14" t="s">
         <v>314</v>
       </c>
       <c r="D140" t="s">
@@ -6219,13 +6292,13 @@
       </c>
     </row>
     <row r="141" ht="14" customHeight="1" spans="1:4">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B141" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C141" s="8" t="s">
+      <c r="C141" s="14" t="s">
         <v>316</v>
       </c>
       <c r="D141" t="s">
@@ -6233,13 +6306,13 @@
       </c>
     </row>
     <row r="142" ht="14" customHeight="1" spans="1:4">
-      <c r="A142" s="8" t="s">
+      <c r="A142" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C142" s="8" t="s">
+      <c r="C142" s="14" t="s">
         <v>319</v>
       </c>
       <c r="D142" t="s">
@@ -6247,13 +6320,13 @@
       </c>
     </row>
     <row r="143" ht="14" customHeight="1" spans="1:4">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C143" s="8" t="s">
+      <c r="C143" s="14" t="s">
         <v>321</v>
       </c>
       <c r="D143" t="s">
@@ -6261,13 +6334,13 @@
       </c>
     </row>
     <row r="144" ht="14" customHeight="1" spans="1:4">
-      <c r="A144" s="8" t="s">
+      <c r="A144" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="C144" s="14" t="s">
         <v>323</v>
       </c>
       <c r="D144" t="s">
@@ -6275,13 +6348,13 @@
       </c>
     </row>
     <row r="145" ht="14" customHeight="1" spans="1:4">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B145" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C145" s="8" t="s">
+      <c r="C145" s="14" t="s">
         <v>325</v>
       </c>
       <c r="D145" t="s">
@@ -6289,13 +6362,13 @@
       </c>
     </row>
     <row r="146" ht="14" customHeight="1" spans="1:4">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="C146" s="14" t="s">
         <v>327</v>
       </c>
       <c r="D146" t="s">
@@ -6303,13 +6376,13 @@
       </c>
     </row>
     <row r="147" ht="14" customHeight="1" spans="1:4">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B147" s="8" t="s">
+      <c r="B147" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C147" s="8" t="s">
+      <c r="C147" s="14" t="s">
         <v>330</v>
       </c>
       <c r="D147" t="s">
@@ -6317,13 +6390,13 @@
       </c>
     </row>
     <row r="148" ht="14" customHeight="1" spans="1:4">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="C148" s="14" t="s">
         <v>332</v>
       </c>
       <c r="D148" t="s">
@@ -6331,13 +6404,13 @@
       </c>
     </row>
     <row r="149" ht="14" customHeight="1" spans="1:4">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C149" s="14" t="s">
         <v>334</v>
       </c>
       <c r="D149" t="s">
@@ -6345,13 +6418,13 @@
       </c>
     </row>
     <row r="150" ht="14" customHeight="1" spans="1:4">
-      <c r="A150" s="8" t="s">
+      <c r="A150" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C150" s="8" t="s">
+      <c r="C150" s="14" t="s">
         <v>336</v>
       </c>
       <c r="D150" t="s">
@@ -6359,13 +6432,13 @@
       </c>
     </row>
     <row r="151" ht="14" customHeight="1" spans="1:4">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="14" t="s">
         <v>329</v>
       </c>
-      <c r="C151" s="8" t="s">
+      <c r="C151" s="14" t="s">
         <v>338</v>
       </c>
       <c r="D151" t="s">
@@ -6373,13 +6446,13 @@
       </c>
     </row>
     <row r="152" ht="14" customHeight="1" spans="1:4">
-      <c r="A152" s="8" t="s">
+      <c r="A152" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C152" s="8" t="s">
+      <c r="C152" s="14" t="s">
         <v>341</v>
       </c>
       <c r="D152" t="s">
@@ -6387,13 +6460,13 @@
       </c>
     </row>
     <row r="153" ht="14" customHeight="1" spans="1:4">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C153" s="8" t="s">
+      <c r="C153" s="14" t="s">
         <v>343</v>
       </c>
       <c r="D153" t="s">
@@ -6401,13 +6474,13 @@
       </c>
     </row>
     <row r="154" ht="14" customHeight="1" spans="1:4">
-      <c r="A154" s="8" t="s">
+      <c r="A154" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C154" s="8" t="s">
+      <c r="C154" s="14" t="s">
         <v>345</v>
       </c>
       <c r="D154" t="s">
@@ -6415,13 +6488,13 @@
       </c>
     </row>
     <row r="155" ht="14" customHeight="1" spans="1:4">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C155" s="8" t="s">
+      <c r="C155" s="14" t="s">
         <v>347</v>
       </c>
       <c r="D155" t="s">
@@ -6429,13 +6502,13 @@
       </c>
     </row>
     <row r="156" ht="14" customHeight="1" spans="1:4">
-      <c r="A156" s="8" t="s">
+      <c r="A156" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="14" t="s">
         <v>340</v>
       </c>
-      <c r="C156" s="8" t="s">
+      <c r="C156" s="14" t="s">
         <v>349</v>
       </c>
       <c r="D156" t="s">
@@ -6443,13 +6516,13 @@
       </c>
     </row>
     <row r="157" ht="14" customHeight="1" spans="1:4">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C157" s="8" t="s">
+      <c r="C157" s="14" t="s">
         <v>353</v>
       </c>
       <c r="D157" t="s">
@@ -6457,13 +6530,13 @@
       </c>
     </row>
     <row r="158" ht="14" customHeight="1" spans="1:4">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C158" s="8" t="s">
+      <c r="C158" s="14" t="s">
         <v>355</v>
       </c>
       <c r="D158" t="s">
@@ -6471,13 +6544,13 @@
       </c>
     </row>
     <row r="159" ht="14" customHeight="1" spans="1:4">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C159" s="8" t="s">
+      <c r="C159" s="14" t="s">
         <v>357</v>
       </c>
       <c r="D159" t="s">
@@ -6485,13 +6558,13 @@
       </c>
     </row>
     <row r="160" ht="14" customHeight="1" spans="1:4">
-      <c r="A160" s="8" t="s">
+      <c r="A160" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C160" s="8" t="s">
+      <c r="C160" s="14" t="s">
         <v>359</v>
       </c>
       <c r="D160" t="s">
@@ -6499,13 +6572,13 @@
       </c>
     </row>
     <row r="161" ht="14" customHeight="1" spans="1:4">
-      <c r="A161" s="8" t="s">
+      <c r="A161" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="C161" s="8" t="s">
+      <c r="C161" s="14" t="s">
         <v>361</v>
       </c>
       <c r="D161" t="s">
@@ -6513,13 +6586,13 @@
       </c>
     </row>
     <row r="162" ht="14" customHeight="1" spans="1:4">
-      <c r="A162" s="8" t="s">
+      <c r="A162" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C162" s="8" t="s">
+      <c r="C162" s="14" t="s">
         <v>364</v>
       </c>
       <c r="D162" t="s">
@@ -6527,13 +6600,13 @@
       </c>
     </row>
     <row r="163" ht="14" customHeight="1" spans="1:4">
-      <c r="A163" s="8" t="s">
+      <c r="A163" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C163" s="8" t="s">
+      <c r="C163" s="14" t="s">
         <v>366</v>
       </c>
       <c r="D163" t="s">
@@ -6541,13 +6614,13 @@
       </c>
     </row>
     <row r="164" ht="14" customHeight="1" spans="1:4">
-      <c r="A164" s="8" t="s">
+      <c r="A164" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C164" s="8" t="s">
+      <c r="C164" s="14" t="s">
         <v>368</v>
       </c>
       <c r="D164" t="s">
@@ -6555,13 +6628,13 @@
       </c>
     </row>
     <row r="165" ht="14" customHeight="1" spans="1:4">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C165" s="8" t="s">
+      <c r="C165" s="14" t="s">
         <v>370</v>
       </c>
       <c r="D165" t="s">
@@ -6569,13 +6642,13 @@
       </c>
     </row>
     <row r="166" ht="14" customHeight="1" spans="1:4">
-      <c r="A166" s="8" t="s">
+      <c r="A166" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="B166" s="14" t="s">
         <v>363</v>
       </c>
-      <c r="C166" s="8" t="s">
+      <c r="C166" s="14" t="s">
         <v>372</v>
       </c>
       <c r="D166" t="s">
@@ -6583,13 +6656,13 @@
       </c>
     </row>
     <row r="167" ht="14" customHeight="1" spans="1:4">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B167" s="8" t="s">
+      <c r="B167" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C167" s="8" t="s">
+      <c r="C167" s="14" t="s">
         <v>375</v>
       </c>
       <c r="D167" t="s">
@@ -6597,13 +6670,13 @@
       </c>
     </row>
     <row r="168" ht="14" customHeight="1" spans="1:4">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="B168" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C168" s="8" t="s">
+      <c r="C168" s="14" t="s">
         <v>377</v>
       </c>
       <c r="D168" t="s">
@@ -6611,13 +6684,13 @@
       </c>
     </row>
     <row r="169" ht="14" customHeight="1" spans="1:4">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C169" s="8" t="s">
+      <c r="C169" s="14" t="s">
         <v>379</v>
       </c>
       <c r="D169" t="s">
@@ -6625,13 +6698,13 @@
       </c>
     </row>
     <row r="170" ht="14" customHeight="1" spans="1:4">
-      <c r="A170" s="8" t="s">
+      <c r="A170" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="B170" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C170" s="8" t="s">
+      <c r="C170" s="14" t="s">
         <v>381</v>
       </c>
       <c r="D170" t="s">
@@ -6639,13 +6712,13 @@
       </c>
     </row>
     <row r="171" ht="14" customHeight="1" spans="1:4">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="14" t="s">
         <v>374</v>
       </c>
-      <c r="C171" s="8" t="s">
+      <c r="C171" s="14" t="s">
         <v>383</v>
       </c>
       <c r="D171" t="s">
@@ -6653,13 +6726,13 @@
       </c>
     </row>
     <row r="172" ht="14" customHeight="1" spans="1:4">
-      <c r="A172" s="8" t="s">
+      <c r="A172" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C172" s="8" t="s">
+      <c r="C172" s="14" t="s">
         <v>386</v>
       </c>
       <c r="D172" t="s">
@@ -6667,13 +6740,13 @@
       </c>
     </row>
     <row r="173" ht="14" customHeight="1" spans="1:4">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B173" s="8" t="s">
+      <c r="B173" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C173" s="8" t="s">
+      <c r="C173" s="14" t="s">
         <v>388</v>
       </c>
       <c r="D173" t="s">
@@ -6681,13 +6754,13 @@
       </c>
     </row>
     <row r="174" ht="14" customHeight="1" spans="1:4">
-      <c r="A174" s="8" t="s">
+      <c r="A174" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B174" s="8" t="s">
+      <c r="B174" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C174" s="8" t="s">
+      <c r="C174" s="14" t="s">
         <v>390</v>
       </c>
       <c r="D174" t="s">
@@ -6695,13 +6768,13 @@
       </c>
     </row>
     <row r="175" ht="14" customHeight="1" spans="1:4">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B175" s="8" t="s">
+      <c r="B175" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C175" s="8" t="s">
+      <c r="C175" s="14" t="s">
         <v>392</v>
       </c>
       <c r="D175" t="s">
@@ -6709,13 +6782,13 @@
       </c>
     </row>
     <row r="176" ht="14" customHeight="1" spans="1:4">
-      <c r="A176" s="8" t="s">
+      <c r="A176" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B176" s="8" t="s">
+      <c r="B176" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="C176" s="8" t="s">
+      <c r="C176" s="14" t="s">
         <v>394</v>
       </c>
       <c r="D176" t="s">
@@ -6723,13 +6796,13 @@
       </c>
     </row>
     <row r="177" ht="14" customHeight="1" spans="1:4">
-      <c r="A177" s="8" t="s">
+      <c r="A177" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B177" s="8" t="s">
+      <c r="B177" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="14" t="s">
         <v>397</v>
       </c>
       <c r="D177" t="s">
@@ -6737,13 +6810,13 @@
       </c>
     </row>
     <row r="178" ht="14" customHeight="1" spans="1:4">
-      <c r="A178" s="8" t="s">
+      <c r="A178" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B178" s="8" t="s">
+      <c r="B178" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="14" t="s">
         <v>399</v>
       </c>
       <c r="D178" t="s">
@@ -6751,13 +6824,13 @@
       </c>
     </row>
     <row r="179" ht="14" customHeight="1" spans="1:4">
-      <c r="A179" s="8" t="s">
+      <c r="A179" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B179" s="8" t="s">
+      <c r="B179" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="14" t="s">
         <v>401</v>
       </c>
       <c r="D179" t="s">
@@ -6765,13 +6838,13 @@
       </c>
     </row>
     <row r="180" ht="14" customHeight="1" spans="1:4">
-      <c r="A180" s="8" t="s">
+      <c r="A180" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="B180" s="8" t="s">
+      <c r="B180" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="14" t="s">
         <v>403</v>
       </c>
       <c r="D180" t="s">
@@ -6779,13 +6852,13 @@
       </c>
     </row>
     <row r="181" ht="14" customHeight="1" spans="1:4">
-      <c r="A181" s="8" t="s">
+      <c r="A181" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B181" s="8" t="s">
+      <c r="B181" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="14" t="s">
         <v>407</v>
       </c>
       <c r="D181" t="s">
@@ -6793,13 +6866,13 @@
       </c>
     </row>
     <row r="182" ht="14" customHeight="1" spans="1:4">
-      <c r="A182" s="8" t="s">
+      <c r="A182" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B182" s="8" t="s">
+      <c r="B182" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="14" t="s">
         <v>409</v>
       </c>
       <c r="D182" t="s">
@@ -6807,13 +6880,13 @@
       </c>
     </row>
     <row r="183" ht="14" customHeight="1" spans="1:4">
-      <c r="A183" s="8" t="s">
+      <c r="A183" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="8" t="s">
+      <c r="B183" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="14" t="s">
         <v>411</v>
       </c>
       <c r="D183" t="s">
@@ -6821,13 +6894,13 @@
       </c>
     </row>
     <row r="184" ht="14" customHeight="1" spans="1:4">
-      <c r="A184" s="8" t="s">
+      <c r="A184" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B184" s="8" t="s">
+      <c r="B184" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="14" t="s">
         <v>413</v>
       </c>
       <c r="D184" t="s">
@@ -6835,13 +6908,13 @@
       </c>
     </row>
     <row r="185" ht="14" customHeight="1" spans="1:4">
-      <c r="A185" s="8" t="s">
+      <c r="A185" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B185" s="8" t="s">
+      <c r="B185" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="14" t="s">
         <v>415</v>
       </c>
       <c r="D185" t="s">
@@ -6849,13 +6922,13 @@
       </c>
     </row>
     <row r="186" ht="14" customHeight="1" spans="1:4">
-      <c r="A186" s="8" t="s">
+      <c r="A186" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B186" s="8" t="s">
+      <c r="B186" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="14" t="s">
         <v>417</v>
       </c>
       <c r="D186" t="s">
@@ -6863,13 +6936,13 @@
       </c>
     </row>
     <row r="187" ht="14" customHeight="1" spans="1:4">
-      <c r="A187" s="8" t="s">
+      <c r="A187" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B187" s="8" t="s">
+      <c r="B187" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="14" t="s">
         <v>419</v>
       </c>
       <c r="D187" t="s">
@@ -6877,13 +6950,13 @@
       </c>
     </row>
     <row r="188" ht="14" customHeight="1" spans="1:4">
-      <c r="A188" s="8" t="s">
+      <c r="A188" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B188" s="8" t="s">
+      <c r="B188" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="14" t="s">
         <v>421</v>
       </c>
       <c r="D188" t="s">
@@ -6891,13 +6964,13 @@
       </c>
     </row>
     <row r="189" ht="14" customHeight="1" spans="1:4">
-      <c r="A189" s="8" t="s">
+      <c r="A189" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B189" s="8" t="s">
+      <c r="B189" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="14" t="s">
         <v>423</v>
       </c>
       <c r="D189" t="s">
@@ -6905,13 +6978,13 @@
       </c>
     </row>
     <row r="190" ht="14" customHeight="1" spans="1:4">
-      <c r="A190" s="8" t="s">
+      <c r="A190" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B190" s="8" t="s">
+      <c r="B190" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C190" s="8" t="s">
+      <c r="C190" s="14" t="s">
         <v>425</v>
       </c>
       <c r="D190" t="s">
@@ -6919,13 +6992,13 @@
       </c>
     </row>
     <row r="191" ht="14" customHeight="1" spans="1:4">
-      <c r="A191" s="8" t="s">
+      <c r="A191" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B191" s="8" t="s">
+      <c r="B191" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C191" s="8" t="s">
+      <c r="C191" s="14" t="s">
         <v>428</v>
       </c>
       <c r="D191" t="s">
@@ -6933,13 +7006,13 @@
       </c>
     </row>
     <row r="192" ht="14" customHeight="1" spans="1:4">
-      <c r="A192" s="8" t="s">
+      <c r="A192" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B192" s="8" t="s">
+      <c r="B192" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C192" s="8" t="s">
+      <c r="C192" s="14" t="s">
         <v>430</v>
       </c>
       <c r="D192" t="s">
@@ -6947,13 +7020,13 @@
       </c>
     </row>
     <row r="193" ht="14" customHeight="1" spans="1:4">
-      <c r="A193" s="8" t="s">
+      <c r="A193" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B193" s="8" t="s">
+      <c r="B193" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C193" s="8" t="s">
+      <c r="C193" s="14" t="s">
         <v>432</v>
       </c>
       <c r="D193" t="s">
@@ -6961,13 +7034,13 @@
       </c>
     </row>
     <row r="194" ht="14" customHeight="1" spans="1:4">
-      <c r="A194" s="8" t="s">
+      <c r="A194" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B194" s="8" t="s">
+      <c r="B194" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C194" s="8" t="s">
+      <c r="C194" s="14" t="s">
         <v>434</v>
       </c>
       <c r="D194" t="s">
@@ -6975,13 +7048,13 @@
       </c>
     </row>
     <row r="195" ht="14" customHeight="1" spans="1:4">
-      <c r="A195" s="8" t="s">
+      <c r="A195" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B195" s="8" t="s">
+      <c r="B195" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C195" s="8" t="s">
+      <c r="C195" s="14" t="s">
         <v>436</v>
       </c>
       <c r="D195" t="s">
@@ -6989,13 +7062,13 @@
       </c>
     </row>
     <row r="196" ht="14" customHeight="1" spans="1:4">
-      <c r="A196" s="8" t="s">
+      <c r="A196" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B196" s="8" t="s">
+      <c r="B196" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C196" s="8" t="s">
+      <c r="C196" s="14" t="s">
         <v>439</v>
       </c>
       <c r="D196" t="s">
@@ -7003,13 +7076,13 @@
       </c>
     </row>
     <row r="197" ht="14" customHeight="1" spans="1:4">
-      <c r="A197" s="8" t="s">
+      <c r="A197" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B197" s="8" t="s">
+      <c r="B197" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C197" s="8" t="s">
+      <c r="C197" s="14" t="s">
         <v>441</v>
       </c>
       <c r="D197" t="s">
@@ -7017,13 +7090,13 @@
       </c>
     </row>
     <row r="198" ht="14" customHeight="1" spans="1:4">
-      <c r="A198" s="8" t="s">
+      <c r="A198" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B198" s="8" t="s">
+      <c r="B198" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C198" s="8" t="s">
+      <c r="C198" s="14" t="s">
         <v>443</v>
       </c>
       <c r="D198" t="s">
@@ -7031,13 +7104,13 @@
       </c>
     </row>
     <row r="199" ht="14" customHeight="1" spans="1:4">
-      <c r="A199" s="8" t="s">
+      <c r="A199" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B199" s="8" t="s">
+      <c r="B199" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C199" s="8" t="s">
+      <c r="C199" s="14" t="s">
         <v>445</v>
       </c>
       <c r="D199" t="s">
@@ -7045,13 +7118,13 @@
       </c>
     </row>
     <row r="200" ht="14" customHeight="1" spans="1:4">
-      <c r="A200" s="8" t="s">
+      <c r="A200" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B200" s="8" t="s">
+      <c r="B200" s="14" t="s">
         <v>438</v>
       </c>
-      <c r="C200" s="8" t="s">
+      <c r="C200" s="14" t="s">
         <v>447</v>
       </c>
       <c r="D200" t="s">
@@ -7059,13 +7132,13 @@
       </c>
     </row>
     <row r="201" ht="14" customHeight="1" spans="1:4">
-      <c r="A201" s="8" t="s">
+      <c r="A201" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B201" s="8" t="s">
+      <c r="B201" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C201" s="8" t="s">
+      <c r="C201" s="14" t="s">
         <v>451</v>
       </c>
       <c r="D201" t="s">
@@ -7073,13 +7146,13 @@
       </c>
     </row>
     <row r="202" ht="14" customHeight="1" spans="1:4">
-      <c r="A202" s="8" t="s">
+      <c r="A202" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B202" s="8" t="s">
+      <c r="B202" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C202" s="8" t="s">
+      <c r="C202" s="14" t="s">
         <v>453</v>
       </c>
       <c r="D202" t="s">
@@ -7087,13 +7160,13 @@
       </c>
     </row>
     <row r="203" ht="14" customHeight="1" spans="1:4">
-      <c r="A203" s="8" t="s">
+      <c r="A203" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B203" s="8" t="s">
+      <c r="B203" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C203" s="8" t="s">
+      <c r="C203" s="14" t="s">
         <v>455</v>
       </c>
       <c r="D203" t="s">
@@ -7101,13 +7174,13 @@
       </c>
     </row>
     <row r="204" ht="14" customHeight="1" spans="1:4">
-      <c r="A204" s="8" t="s">
+      <c r="A204" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B204" s="8" t="s">
+      <c r="B204" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C204" s="8" t="s">
+      <c r="C204" s="14" t="s">
         <v>457</v>
       </c>
       <c r="D204" t="s">
@@ -7115,13 +7188,13 @@
       </c>
     </row>
     <row r="205" ht="14" customHeight="1" spans="1:4">
-      <c r="A205" s="8" t="s">
+      <c r="A205" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B205" s="8" t="s">
+      <c r="B205" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="14" t="s">
         <v>459</v>
       </c>
       <c r="D205" t="s">
@@ -7129,13 +7202,13 @@
       </c>
     </row>
     <row r="206" ht="14" customHeight="1" spans="1:4">
-      <c r="A206" s="8" t="s">
+      <c r="A206" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B206" s="8" t="s">
+      <c r="B206" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C206" s="8" t="s">
+      <c r="C206" s="14" t="s">
         <v>462</v>
       </c>
       <c r="D206" t="s">
@@ -7143,13 +7216,13 @@
       </c>
     </row>
     <row r="207" ht="14" customHeight="1" spans="1:4">
-      <c r="A207" s="8" t="s">
+      <c r="A207" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B207" s="8" t="s">
+      <c r="B207" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C207" s="8" t="s">
+      <c r="C207" s="14" t="s">
         <v>464</v>
       </c>
       <c r="D207" t="s">
@@ -7157,13 +7230,13 @@
       </c>
     </row>
     <row r="208" ht="14" customHeight="1" spans="1:4">
-      <c r="A208" s="8" t="s">
+      <c r="A208" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B208" s="8" t="s">
+      <c r="B208" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C208" s="8" t="s">
+      <c r="C208" s="14" t="s">
         <v>466</v>
       </c>
       <c r="D208" t="s">
@@ -7171,13 +7244,13 @@
       </c>
     </row>
     <row r="209" ht="14" customHeight="1" spans="1:4">
-      <c r="A209" s="8" t="s">
+      <c r="A209" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B209" s="8" t="s">
+      <c r="B209" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C209" s="8" t="s">
+      <c r="C209" s="14" t="s">
         <v>468</v>
       </c>
       <c r="D209" t="s">
@@ -7185,13 +7258,13 @@
       </c>
     </row>
     <row r="210" ht="14" customHeight="1" spans="1:4">
-      <c r="A210" s="8" t="s">
+      <c r="A210" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B210" s="8" t="s">
+      <c r="B210" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C210" s="8" t="s">
+      <c r="C210" s="14" t="s">
         <v>470</v>
       </c>
       <c r="D210" t="s">
@@ -7199,13 +7272,13 @@
       </c>
     </row>
     <row r="211" ht="14" customHeight="1" spans="1:4">
-      <c r="A211" s="8" t="s">
+      <c r="A211" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B211" s="8" t="s">
+      <c r="B211" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="C211" s="8" t="s">
+      <c r="C211" s="14" t="s">
         <v>472</v>
       </c>
       <c r="D211" t="s">
@@ -7213,13 +7286,13 @@
       </c>
     </row>
     <row r="212" ht="14" customHeight="1" spans="1:4">
-      <c r="A212" s="8" t="s">
+      <c r="A212" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B212" s="8" t="s">
+      <c r="B212" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C212" s="8" t="s">
+      <c r="C212" s="14" t="s">
         <v>475</v>
       </c>
       <c r="D212" t="s">
@@ -7227,13 +7300,13 @@
       </c>
     </row>
     <row r="213" ht="14" customHeight="1" spans="1:4">
-      <c r="A213" s="8" t="s">
+      <c r="A213" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B213" s="8" t="s">
+      <c r="B213" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C213" s="8" t="s">
+      <c r="C213" s="14" t="s">
         <v>477</v>
       </c>
       <c r="D213" t="s">
@@ -7241,13 +7314,13 @@
       </c>
     </row>
     <row r="214" ht="14" customHeight="1" spans="1:4">
-      <c r="A214" s="8" t="s">
+      <c r="A214" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B214" s="8" t="s">
+      <c r="B214" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C214" s="8" t="s">
+      <c r="C214" s="14" t="s">
         <v>479</v>
       </c>
       <c r="D214" t="s">
@@ -7255,13 +7328,13 @@
       </c>
     </row>
     <row r="215" ht="14" customHeight="1" spans="1:4">
-      <c r="A215" s="8" t="s">
+      <c r="A215" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B215" s="8" t="s">
+      <c r="B215" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C215" s="8" t="s">
+      <c r="C215" s="14" t="s">
         <v>481</v>
       </c>
       <c r="D215" t="s">
@@ -7269,13 +7342,13 @@
       </c>
     </row>
     <row r="216" ht="14" customHeight="1" spans="1:4">
-      <c r="A216" s="8" t="s">
+      <c r="A216" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B216" s="8" t="s">
+      <c r="B216" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C216" s="8" t="s">
+      <c r="C216" s="14" t="s">
         <v>483</v>
       </c>
       <c r="D216" t="s">
@@ -7283,13 +7356,13 @@
       </c>
     </row>
     <row r="217" ht="14" customHeight="1" spans="1:4">
-      <c r="A217" s="8" t="s">
+      <c r="A217" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B217" s="8" t="s">
+      <c r="B217" s="14" t="s">
         <v>474</v>
       </c>
-      <c r="C217" s="8" t="s">
+      <c r="C217" s="14" t="s">
         <v>485</v>
       </c>
       <c r="D217" t="s">
@@ -7297,13 +7370,13 @@
       </c>
     </row>
     <row r="218" ht="14" customHeight="1" spans="1:4">
-      <c r="A218" s="8" t="s">
+      <c r="A218" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B218" s="8" t="s">
+      <c r="B218" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C218" s="8" t="s">
+      <c r="C218" s="14" t="s">
         <v>488</v>
       </c>
       <c r="D218" t="s">
@@ -7311,13 +7384,13 @@
       </c>
     </row>
     <row r="219" ht="14" customHeight="1" spans="1:4">
-      <c r="A219" s="8" t="s">
+      <c r="A219" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B219" s="8" t="s">
+      <c r="B219" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C219" s="8" t="s">
+      <c r="C219" s="14" t="s">
         <v>490</v>
       </c>
       <c r="D219" t="s">
@@ -7325,13 +7398,13 @@
       </c>
     </row>
     <row r="220" ht="14" customHeight="1" spans="1:4">
-      <c r="A220" s="8" t="s">
+      <c r="A220" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B220" s="8" t="s">
+      <c r="B220" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C220" s="8" t="s">
+      <c r="C220" s="14" t="s">
         <v>492</v>
       </c>
       <c r="D220" t="s">
@@ -7339,13 +7412,13 @@
       </c>
     </row>
     <row r="221" ht="14" customHeight="1" spans="1:4">
-      <c r="A221" s="8" t="s">
+      <c r="A221" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B221" s="8" t="s">
+      <c r="B221" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C221" s="8" t="s">
+      <c r="C221" s="14" t="s">
         <v>494</v>
       </c>
       <c r="D221" t="s">
@@ -7353,13 +7426,13 @@
       </c>
     </row>
     <row r="222" ht="14" customHeight="1" spans="1:4">
-      <c r="A222" s="8" t="s">
+      <c r="A222" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B222" s="8" t="s">
+      <c r="B222" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C222" s="8" t="s">
+      <c r="C222" s="14" t="s">
         <v>496</v>
       </c>
       <c r="D222" t="s">
@@ -7367,13 +7440,13 @@
       </c>
     </row>
     <row r="223" ht="14" customHeight="1" spans="1:4">
-      <c r="A223" s="8" t="s">
+      <c r="A223" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B223" s="8" t="s">
+      <c r="B223" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="C223" s="8" t="s">
+      <c r="C223" s="14" t="s">
         <v>498</v>
       </c>
       <c r="D223" t="s">
@@ -7381,13 +7454,13 @@
       </c>
     </row>
     <row r="224" ht="14" customHeight="1" spans="1:4">
-      <c r="A224" s="8" t="s">
+      <c r="A224" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B224" s="8" t="s">
+      <c r="B224" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C224" s="8" t="s">
+      <c r="C224" s="14" t="s">
         <v>501</v>
       </c>
       <c r="D224" t="s">
@@ -7395,13 +7468,13 @@
       </c>
     </row>
     <row r="225" ht="14" customHeight="1" spans="1:4">
-      <c r="A225" s="8" t="s">
+      <c r="A225" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B225" s="8" t="s">
+      <c r="B225" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C225" s="8" t="s">
+      <c r="C225" s="14" t="s">
         <v>503</v>
       </c>
       <c r="D225" t="s">
@@ -7409,13 +7482,13 @@
       </c>
     </row>
     <row r="226" ht="14" customHeight="1" spans="1:4">
-      <c r="A226" s="8" t="s">
+      <c r="A226" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B226" s="8" t="s">
+      <c r="B226" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C226" s="8" t="s">
+      <c r="C226" s="14" t="s">
         <v>505</v>
       </c>
       <c r="D226" t="s">
@@ -7423,13 +7496,13 @@
       </c>
     </row>
     <row r="227" ht="14" customHeight="1" spans="1:4">
-      <c r="A227" s="8" t="s">
+      <c r="A227" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B227" s="8" t="s">
+      <c r="B227" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C227" s="8" t="s">
+      <c r="C227" s="14" t="s">
         <v>507</v>
       </c>
       <c r="D227" t="s">
@@ -7437,13 +7510,13 @@
       </c>
     </row>
     <row r="228" ht="14" customHeight="1" spans="1:4">
-      <c r="A228" s="8" t="s">
+      <c r="A228" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B228" s="8" t="s">
+      <c r="B228" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C228" s="8" t="s">
+      <c r="C228" s="14" t="s">
         <v>509</v>
       </c>
       <c r="D228" t="s">
@@ -7451,13 +7524,13 @@
       </c>
     </row>
     <row r="229" ht="14" customHeight="1" spans="1:4">
-      <c r="A229" s="8" t="s">
+      <c r="A229" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B229" s="8" t="s">
+      <c r="B229" s="14" t="s">
         <v>500</v>
       </c>
-      <c r="C229" s="8" t="s">
+      <c r="C229" s="14" t="s">
         <v>511</v>
       </c>
       <c r="D229" t="s">
@@ -7465,13 +7538,13 @@
       </c>
     </row>
     <row r="230" ht="14" customHeight="1" spans="1:4">
-      <c r="A230" s="8" t="s">
+      <c r="A230" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B230" s="8" t="s">
+      <c r="B230" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="C230" s="8" t="s">
+      <c r="C230" s="14" t="s">
         <v>514</v>
       </c>
       <c r="D230" t="s">
@@ -7479,13 +7552,13 @@
       </c>
     </row>
     <row r="231" ht="14" customHeight="1" spans="1:4">
-      <c r="A231" s="8" t="s">
+      <c r="A231" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B231" s="8" t="s">
+      <c r="B231" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="C231" s="8" t="s">
+      <c r="C231" s="14" t="s">
         <v>516</v>
       </c>
       <c r="D231" t="s">
@@ -7493,13 +7566,13 @@
       </c>
     </row>
     <row r="232" ht="14" customHeight="1" spans="1:4">
-      <c r="A232" s="8" t="s">
+      <c r="A232" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B232" s="8" t="s">
+      <c r="B232" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="C232" s="8" t="s">
+      <c r="C232" s="14" t="s">
         <v>518</v>
       </c>
       <c r="D232" t="s">
@@ -7507,13 +7580,13 @@
       </c>
     </row>
     <row r="233" ht="14" customHeight="1" spans="1:4">
-      <c r="A233" s="8" t="s">
+      <c r="A233" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B233" s="8" t="s">
+      <c r="B233" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="C233" s="8" t="s">
+      <c r="C233" s="14" t="s">
         <v>520</v>
       </c>
       <c r="D233" t="s">
@@ -7521,13 +7594,13 @@
       </c>
     </row>
     <row r="234" ht="14" customHeight="1" spans="1:4">
-      <c r="A234" s="8" t="s">
+      <c r="A234" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="B234" s="8" t="s">
+      <c r="B234" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="C234" s="8" t="s">
+      <c r="C234" s="14" t="s">
         <v>522</v>
       </c>
       <c r="D234" t="s">
@@ -7535,13 +7608,13 @@
       </c>
     </row>
     <row r="235" ht="14" customHeight="1" spans="1:4">
-      <c r="A235" s="8" t="s">
+      <c r="A235" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B235" s="8" t="s">
+      <c r="B235" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="C235" s="8" t="s">
+      <c r="C235" s="14" t="s">
         <v>526</v>
       </c>
       <c r="D235" t="s">
@@ -7549,13 +7622,13 @@
       </c>
     </row>
     <row r="236" ht="14" customHeight="1" spans="1:4">
-      <c r="A236" s="8" t="s">
+      <c r="A236" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B236" s="8" t="s">
+      <c r="B236" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="C236" s="8" t="s">
+      <c r="C236" s="14" t="s">
         <v>528</v>
       </c>
       <c r="D236" t="s">
@@ -7563,13 +7636,13 @@
       </c>
     </row>
     <row r="237" ht="14" customHeight="1" spans="1:4">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B237" s="8" t="s">
+      <c r="B237" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="C237" s="14" t="s">
         <v>530</v>
       </c>
       <c r="D237" t="s">
@@ -7577,13 +7650,13 @@
       </c>
     </row>
     <row r="238" ht="14" customHeight="1" spans="1:4">
-      <c r="A238" s="8" t="s">
+      <c r="A238" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B238" s="8" t="s">
+      <c r="B238" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="C238" s="8" t="s">
+      <c r="C238" s="14" t="s">
         <v>532</v>
       </c>
       <c r="D238" t="s">
@@ -7591,13 +7664,13 @@
       </c>
     </row>
     <row r="239" ht="14" customHeight="1" spans="1:4">
-      <c r="A239" s="8" t="s">
+      <c r="A239" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B239" s="8" t="s">
+      <c r="B239" s="14" t="s">
         <v>525</v>
       </c>
-      <c r="C239" s="8" t="s">
+      <c r="C239" s="14" t="s">
         <v>534</v>
       </c>
       <c r="D239" t="s">
@@ -7605,13 +7678,13 @@
       </c>
     </row>
     <row r="240" ht="14" customHeight="1" spans="1:4">
-      <c r="A240" s="8" t="s">
+      <c r="A240" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B240" s="8" t="s">
+      <c r="B240" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C240" s="8" t="s">
+      <c r="C240" s="14" t="s">
         <v>537</v>
       </c>
       <c r="D240" t="s">
@@ -7619,13 +7692,13 @@
       </c>
     </row>
     <row r="241" ht="14" customHeight="1" spans="1:4">
-      <c r="A241" s="8" t="s">
+      <c r="A241" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B241" s="8" t="s">
+      <c r="B241" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C241" s="8" t="s">
+      <c r="C241" s="14" t="s">
         <v>539</v>
       </c>
       <c r="D241" t="s">
@@ -7633,13 +7706,13 @@
       </c>
     </row>
     <row r="242" ht="14" customHeight="1" spans="1:4">
-      <c r="A242" s="8" t="s">
+      <c r="A242" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B242" s="8" t="s">
+      <c r="B242" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C242" s="8" t="s">
+      <c r="C242" s="14" t="s">
         <v>541</v>
       </c>
       <c r="D242" t="s">
@@ -7647,13 +7720,13 @@
       </c>
     </row>
     <row r="243" ht="14" customHeight="1" spans="1:4">
-      <c r="A243" s="8" t="s">
+      <c r="A243" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B243" s="8" t="s">
+      <c r="B243" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C243" s="8" t="s">
+      <c r="C243" s="14" t="s">
         <v>543</v>
       </c>
       <c r="D243" t="s">
@@ -7661,13 +7734,13 @@
       </c>
     </row>
     <row r="244" ht="14" customHeight="1" spans="1:4">
-      <c r="A244" s="8" t="s">
+      <c r="A244" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B244" s="8" t="s">
+      <c r="B244" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C244" s="8" t="s">
+      <c r="C244" s="14" t="s">
         <v>545</v>
       </c>
       <c r="D244" t="s">
@@ -7675,13 +7748,13 @@
       </c>
     </row>
     <row r="245" ht="14" customHeight="1" spans="1:4">
-      <c r="A245" s="8" t="s">
+      <c r="A245" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B245" s="8" t="s">
+      <c r="B245" s="14" t="s">
         <v>536</v>
       </c>
-      <c r="C245" s="8" t="s">
+      <c r="C245" s="14" t="s">
         <v>547</v>
       </c>
       <c r="D245" t="s">
@@ -7689,13 +7762,13 @@
       </c>
     </row>
     <row r="246" ht="14" customHeight="1" spans="1:4">
-      <c r="A246" s="8" t="s">
+      <c r="A246" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B246" s="8" t="s">
+      <c r="B246" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="C246" s="8" t="s">
+      <c r="C246" s="14" t="s">
         <v>550</v>
       </c>
       <c r="D246" t="s">
@@ -7703,13 +7776,13 @@
       </c>
     </row>
     <row r="247" ht="14" customHeight="1" spans="1:4">
-      <c r="A247" s="8" t="s">
+      <c r="A247" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B247" s="8" t="s">
+      <c r="B247" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="C247" s="8" t="s">
+      <c r="C247" s="14" t="s">
         <v>552</v>
       </c>
       <c r="D247" t="s">
@@ -7717,13 +7790,13 @@
       </c>
     </row>
     <row r="248" ht="14" customHeight="1" spans="1:4">
-      <c r="A248" s="8" t="s">
+      <c r="A248" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B248" s="8" t="s">
+      <c r="B248" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="C248" s="8" t="s">
+      <c r="C248" s="14" t="s">
         <v>554</v>
       </c>
       <c r="D248" t="s">
@@ -7731,13 +7804,13 @@
       </c>
     </row>
     <row r="249" ht="14" customHeight="1" spans="1:4">
-      <c r="A249" s="8" t="s">
+      <c r="A249" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B249" s="8" t="s">
+      <c r="B249" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="C249" s="8" t="s">
+      <c r="C249" s="14" t="s">
         <v>556</v>
       </c>
       <c r="D249" t="s">
@@ -7745,13 +7818,13 @@
       </c>
     </row>
     <row r="250" ht="14" customHeight="1" spans="1:4">
-      <c r="A250" s="8" t="s">
+      <c r="A250" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B250" s="8" t="s">
+      <c r="B250" s="14" t="s">
         <v>549</v>
       </c>
-      <c r="C250" s="8" t="s">
+      <c r="C250" s="14" t="s">
         <v>558</v>
       </c>
       <c r="D250" t="s">
@@ -7759,13 +7832,13 @@
       </c>
     </row>
     <row r="251" ht="14" customHeight="1" spans="1:4">
-      <c r="A251" s="8" t="s">
+      <c r="A251" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B251" s="8" t="s">
+      <c r="B251" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="C251" s="8" t="s">
+      <c r="C251" s="14" t="s">
         <v>560</v>
       </c>
       <c r="D251" t="s">
@@ -7773,13 +7846,13 @@
       </c>
     </row>
     <row r="252" ht="14" customHeight="1" spans="1:4">
-      <c r="A252" s="8" t="s">
+      <c r="A252" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B252" s="8" t="s">
+      <c r="B252" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="C252" s="8" t="s">
+      <c r="C252" s="14" t="s">
         <v>562</v>
       </c>
       <c r="D252" t="s">
@@ -7787,13 +7860,13 @@
       </c>
     </row>
     <row r="253" ht="14" customHeight="1" spans="1:4">
-      <c r="A253" s="8" t="s">
+      <c r="A253" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B253" s="8" t="s">
+      <c r="B253" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="C253" s="8" t="s">
+      <c r="C253" s="14" t="s">
         <v>564</v>
       </c>
       <c r="D253" t="s">
@@ -7801,13 +7874,13 @@
       </c>
     </row>
     <row r="254" ht="14" customHeight="1" spans="1:4">
-      <c r="A254" s="8" t="s">
+      <c r="A254" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B254" s="8" t="s">
+      <c r="B254" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="C254" s="8" t="s">
+      <c r="C254" s="14" t="s">
         <v>566</v>
       </c>
       <c r="D254" t="s">
@@ -7815,13 +7888,13 @@
       </c>
     </row>
     <row r="255" ht="14" customHeight="1" spans="1:4">
-      <c r="A255" s="8" t="s">
+      <c r="A255" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B255" s="8" t="s">
+      <c r="B255" s="14" t="s">
         <v>526</v>
       </c>
-      <c r="C255" s="8" t="s">
+      <c r="C255" s="14" t="s">
         <v>568</v>
       </c>
       <c r="D255" t="s">
@@ -7829,13 +7902,13 @@
       </c>
     </row>
     <row r="256" ht="14" customHeight="1" spans="1:4">
-      <c r="A256" s="8" t="s">
+      <c r="A256" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B256" s="8" t="s">
+      <c r="B256" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="C256" s="8" t="s">
+      <c r="C256" s="14" t="s">
         <v>571</v>
       </c>
       <c r="D256" t="s">
@@ -7843,13 +7916,13 @@
       </c>
     </row>
     <row r="257" ht="14" customHeight="1" spans="1:4">
-      <c r="A257" s="8" t="s">
+      <c r="A257" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="C257" s="8" t="s">
+      <c r="C257" s="14" t="s">
         <v>573</v>
       </c>
       <c r="D257" t="s">
@@ -7857,13 +7930,13 @@
       </c>
     </row>
     <row r="258" ht="14" customHeight="1" spans="1:4">
-      <c r="A258" s="8" t="s">
+      <c r="A258" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B258" s="8" t="s">
+      <c r="B258" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="C258" s="8" t="s">
+      <c r="C258" s="14" t="s">
         <v>575</v>
       </c>
       <c r="D258" t="s">
@@ -7871,13 +7944,13 @@
       </c>
     </row>
     <row r="259" ht="14" customHeight="1" spans="1:4">
-      <c r="A259" s="8" t="s">
+      <c r="A259" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B259" s="8" t="s">
+      <c r="B259" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="C259" s="8" t="s">
+      <c r="C259" s="14" t="s">
         <v>577</v>
       </c>
       <c r="D259" t="s">
@@ -7885,13 +7958,13 @@
       </c>
     </row>
     <row r="260" ht="14" customHeight="1" spans="1:4">
-      <c r="A260" s="8" t="s">
+      <c r="A260" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B260" s="8" t="s">
+      <c r="B260" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="C260" s="8" t="s">
+      <c r="C260" s="14" t="s">
         <v>579</v>
       </c>
       <c r="D260" t="s">
@@ -7899,13 +7972,13 @@
       </c>
     </row>
     <row r="261" ht="14" customHeight="1" spans="1:4">
-      <c r="A261" s="8" t="s">
+      <c r="A261" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B261" s="8" t="s">
+      <c r="B261" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="C261" s="8" t="s">
+      <c r="C261" s="14" t="s">
         <v>582</v>
       </c>
       <c r="D261" t="s">
@@ -7913,13 +7986,13 @@
       </c>
     </row>
     <row r="262" ht="14" customHeight="1" spans="1:4">
-      <c r="A262" s="8" t="s">
+      <c r="A262" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B262" s="8" t="s">
+      <c r="B262" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="C262" s="8" t="s">
+      <c r="C262" s="14" t="s">
         <v>584</v>
       </c>
       <c r="D262" t="s">
@@ -7927,13 +8000,13 @@
       </c>
     </row>
     <row r="263" ht="14" customHeight="1" spans="1:4">
-      <c r="A263" s="8" t="s">
+      <c r="A263" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B263" s="8" t="s">
+      <c r="B263" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="C263" s="8" t="s">
+      <c r="C263" s="14" t="s">
         <v>586</v>
       </c>
       <c r="D263" t="s">
@@ -7941,13 +8014,13 @@
       </c>
     </row>
     <row r="264" ht="14" customHeight="1" spans="1:4">
-      <c r="A264" s="8" t="s">
+      <c r="A264" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B264" s="8" t="s">
+      <c r="B264" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="C264" s="8" t="s">
+      <c r="C264" s="14" t="s">
         <v>588</v>
       </c>
       <c r="D264" t="s">
@@ -7955,13 +8028,13 @@
       </c>
     </row>
     <row r="265" ht="14" customHeight="1" spans="1:4">
-      <c r="A265" s="8" t="s">
+      <c r="A265" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="B265" s="8" t="s">
+      <c r="B265" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="C265" s="8" t="s">
+      <c r="C265" s="14" t="s">
         <v>590</v>
       </c>
       <c r="D265" t="s">
@@ -7969,13 +8042,13 @@
       </c>
     </row>
     <row r="266" ht="14" customHeight="1" spans="1:4">
-      <c r="A266" s="8" t="s">
+      <c r="A266" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B266" s="8" t="s">
+      <c r="B266" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="C266" s="8" t="s">
+      <c r="C266" s="14" t="s">
         <v>594</v>
       </c>
       <c r="D266" t="s">
@@ -7983,13 +8056,13 @@
       </c>
     </row>
     <row r="267" ht="14" customHeight="1" spans="1:4">
-      <c r="A267" s="8" t="s">
+      <c r="A267" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B267" s="8" t="s">
+      <c r="B267" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="C267" s="8" t="s">
+      <c r="C267" s="14" t="s">
         <v>596</v>
       </c>
       <c r="D267" t="s">
@@ -7997,13 +8070,13 @@
       </c>
     </row>
     <row r="268" ht="14" customHeight="1" spans="1:4">
-      <c r="A268" s="8" t="s">
+      <c r="A268" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B268" s="8" t="s">
+      <c r="B268" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="C268" s="8" t="s">
+      <c r="C268" s="14" t="s">
         <v>598</v>
       </c>
       <c r="D268" t="s">
@@ -8011,13 +8084,13 @@
       </c>
     </row>
     <row r="269" ht="14" customHeight="1" spans="1:4">
-      <c r="A269" s="8" t="s">
+      <c r="A269" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B269" s="8" t="s">
+      <c r="B269" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="C269" s="8" t="s">
+      <c r="C269" s="14" t="s">
         <v>600</v>
       </c>
       <c r="D269" t="s">
@@ -8025,13 +8098,13 @@
       </c>
     </row>
     <row r="270" ht="14" customHeight="1" spans="1:4">
-      <c r="A270" s="8" t="s">
+      <c r="A270" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B270" s="8" t="s">
+      <c r="B270" s="14" t="s">
         <v>593</v>
       </c>
-      <c r="C270" s="8" t="s">
+      <c r="C270" s="14" t="s">
         <v>602</v>
       </c>
       <c r="D270" t="s">
@@ -8039,13 +8112,13 @@
       </c>
     </row>
     <row r="271" ht="14" customHeight="1" spans="1:4">
-      <c r="A271" s="8" t="s">
+      <c r="A271" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B271" s="8" t="s">
+      <c r="B271" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C271" s="8" t="s">
+      <c r="C271" s="14" t="s">
         <v>605</v>
       </c>
       <c r="D271" t="s">
@@ -8053,13 +8126,13 @@
       </c>
     </row>
     <row r="272" ht="14" customHeight="1" spans="1:4">
-      <c r="A272" s="8" t="s">
+      <c r="A272" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B272" s="8" t="s">
+      <c r="B272" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C272" s="8" t="s">
+      <c r="C272" s="14" t="s">
         <v>607</v>
       </c>
       <c r="D272" t="s">
@@ -8067,13 +8140,13 @@
       </c>
     </row>
     <row r="273" ht="14" customHeight="1" spans="1:4">
-      <c r="A273" s="8" t="s">
+      <c r="A273" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B273" s="8" t="s">
+      <c r="B273" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C273" s="8" t="s">
+      <c r="C273" s="14" t="s">
         <v>609</v>
       </c>
       <c r="D273" t="s">
@@ -8081,13 +8154,13 @@
       </c>
     </row>
     <row r="274" ht="14" customHeight="1" spans="1:4">
-      <c r="A274" s="8" t="s">
+      <c r="A274" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B274" s="8" t="s">
+      <c r="B274" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C274" s="8" t="s">
+      <c r="C274" s="14" t="s">
         <v>611</v>
       </c>
       <c r="D274" t="s">
@@ -8095,13 +8168,13 @@
       </c>
     </row>
     <row r="275" ht="14" customHeight="1" spans="1:4">
-      <c r="A275" s="8" t="s">
+      <c r="A275" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B275" s="8" t="s">
+      <c r="B275" s="14" t="s">
         <v>604</v>
       </c>
-      <c r="C275" s="8" t="s">
+      <c r="C275" s="14" t="s">
         <v>613</v>
       </c>
       <c r="D275" t="s">
@@ -8109,13 +8182,13 @@
       </c>
     </row>
     <row r="276" ht="14" customHeight="1" spans="1:4">
-      <c r="A276" s="8" t="s">
+      <c r="A276" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B276" s="8" t="s">
+      <c r="B276" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="C276" s="8" t="s">
+      <c r="C276" s="14" t="s">
         <v>616</v>
       </c>
       <c r="D276" t="s">
@@ -8123,13 +8196,13 @@
       </c>
     </row>
     <row r="277" ht="14" customHeight="1" spans="1:4">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B277" s="8" t="s">
+      <c r="B277" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="C277" s="8" t="s">
+      <c r="C277" s="14" t="s">
         <v>618</v>
       </c>
       <c r="D277" t="s">
@@ -8137,13 +8210,13 @@
       </c>
     </row>
     <row r="278" ht="14" customHeight="1" spans="1:4">
-      <c r="A278" s="8" t="s">
+      <c r="A278" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B278" s="8" t="s">
+      <c r="B278" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="C278" s="8" t="s">
+      <c r="C278" s="14" t="s">
         <v>620</v>
       </c>
       <c r="D278" t="s">
@@ -8151,13 +8224,13 @@
       </c>
     </row>
     <row r="279" ht="14" customHeight="1" spans="1:4">
-      <c r="A279" s="8" t="s">
+      <c r="A279" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B279" s="8" t="s">
+      <c r="B279" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="C279" s="8" t="s">
+      <c r="C279" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D279" t="s">
@@ -8165,13 +8238,13 @@
       </c>
     </row>
     <row r="280" ht="14" customHeight="1" spans="1:4">
-      <c r="A280" s="8" t="s">
+      <c r="A280" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B280" s="8" t="s">
+      <c r="B280" s="14" t="s">
         <v>615</v>
       </c>
-      <c r="C280" s="8" t="s">
+      <c r="C280" s="14" t="s">
         <v>623</v>
       </c>
       <c r="D280" t="s">
@@ -8179,13 +8252,13 @@
       </c>
     </row>
     <row r="281" ht="14" customHeight="1" spans="1:4">
-      <c r="A281" s="8" t="s">
+      <c r="A281" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B281" s="8" t="s">
+      <c r="B281" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="C281" s="8" t="s">
+      <c r="C281" s="14" t="s">
         <v>626</v>
       </c>
       <c r="D281" t="s">
@@ -8193,13 +8266,13 @@
       </c>
     </row>
     <row r="282" ht="14" customHeight="1" spans="1:4">
-      <c r="A282" s="8" t="s">
+      <c r="A282" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B282" s="8" t="s">
+      <c r="B282" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="C282" s="8" t="s">
+      <c r="C282" s="14" t="s">
         <v>628</v>
       </c>
       <c r="D282" t="s">
@@ -8207,13 +8280,13 @@
       </c>
     </row>
     <row r="283" ht="14" customHeight="1" spans="1:4">
-      <c r="A283" s="8" t="s">
+      <c r="A283" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B283" s="8" t="s">
+      <c r="B283" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="C283" s="8" t="s">
+      <c r="C283" s="14" t="s">
         <v>630</v>
       </c>
       <c r="D283" t="s">
@@ -8221,13 +8294,13 @@
       </c>
     </row>
     <row r="284" ht="14" customHeight="1" spans="1:4">
-      <c r="A284" s="8" t="s">
+      <c r="A284" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B284" s="8" t="s">
+      <c r="B284" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="C284" s="8" t="s">
+      <c r="C284" s="14" t="s">
         <v>632</v>
       </c>
       <c r="D284" t="s">
@@ -8235,13 +8308,13 @@
       </c>
     </row>
     <row r="285" ht="14" customHeight="1" spans="1:4">
-      <c r="A285" s="8" t="s">
+      <c r="A285" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B285" s="8" t="s">
+      <c r="B285" s="14" t="s">
         <v>625</v>
       </c>
-      <c r="C285" s="8" t="s">
+      <c r="C285" s="14" t="s">
         <v>634</v>
       </c>
       <c r="D285" t="s">
@@ -8249,13 +8322,13 @@
       </c>
     </row>
     <row r="286" ht="14" customHeight="1" spans="1:4">
-      <c r="A286" s="8" t="s">
+      <c r="A286" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B286" s="8" t="s">
+      <c r="B286" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C286" s="8" t="s">
+      <c r="C286" s="14" t="s">
         <v>637</v>
       </c>
       <c r="D286" t="s">
@@ -8263,13 +8336,13 @@
       </c>
     </row>
     <row r="287" ht="14" customHeight="1" spans="1:4">
-      <c r="A287" s="8" t="s">
+      <c r="A287" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B287" s="8" t="s">
+      <c r="B287" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C287" s="8" t="s">
+      <c r="C287" s="14" t="s">
         <v>639</v>
       </c>
       <c r="D287" t="s">
@@ -8277,13 +8350,13 @@
       </c>
     </row>
     <row r="288" ht="14" customHeight="1" spans="1:4">
-      <c r="A288" s="8" t="s">
+      <c r="A288" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B288" s="8" t="s">
+      <c r="B288" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C288" s="8" t="s">
+      <c r="C288" s="14" t="s">
         <v>641</v>
       </c>
       <c r="D288" t="s">
@@ -8291,13 +8364,13 @@
       </c>
     </row>
     <row r="289" ht="14" customHeight="1" spans="1:4">
-      <c r="A289" s="8" t="s">
+      <c r="A289" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B289" s="8" t="s">
+      <c r="B289" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C289" s="8" t="s">
+      <c r="C289" s="14" t="s">
         <v>643</v>
       </c>
       <c r="D289" t="s">
@@ -8305,13 +8378,13 @@
       </c>
     </row>
     <row r="290" ht="14" customHeight="1" spans="1:4">
-      <c r="A290" s="8" t="s">
+      <c r="A290" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B290" s="8" t="s">
+      <c r="B290" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C290" s="8" t="s">
+      <c r="C290" s="14" t="s">
         <v>645</v>
       </c>
       <c r="D290" t="s">
@@ -8319,13 +8392,13 @@
       </c>
     </row>
     <row r="291" ht="14" customHeight="1" spans="1:4">
-      <c r="A291" s="8" t="s">
+      <c r="A291" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B291" s="8" t="s">
+      <c r="B291" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C291" s="8" t="s">
+      <c r="C291" s="14" t="s">
         <v>648</v>
       </c>
       <c r="D291" t="s">
@@ -8333,13 +8406,13 @@
       </c>
     </row>
     <row r="292" ht="14" customHeight="1" spans="1:4">
-      <c r="A292" s="8" t="s">
+      <c r="A292" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B292" s="8" t="s">
+      <c r="B292" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C292" s="8" t="s">
+      <c r="C292" s="14" t="s">
         <v>650</v>
       </c>
       <c r="D292" t="s">
@@ -8347,13 +8420,13 @@
       </c>
     </row>
     <row r="293" ht="14" customHeight="1" spans="1:4">
-      <c r="A293" s="8" t="s">
+      <c r="A293" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B293" s="8" t="s">
+      <c r="B293" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C293" s="8" t="s">
+      <c r="C293" s="14" t="s">
         <v>652</v>
       </c>
       <c r="D293" t="s">
@@ -8361,13 +8434,13 @@
       </c>
     </row>
     <row r="294" ht="14" customHeight="1" spans="1:4">
-      <c r="A294" s="8" t="s">
+      <c r="A294" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B294" s="8" t="s">
+      <c r="B294" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C294" s="8" t="s">
+      <c r="C294" s="14" t="s">
         <v>654</v>
       </c>
       <c r="D294" t="s">
@@ -8375,13 +8448,13 @@
       </c>
     </row>
     <row r="295" ht="14" customHeight="1" spans="1:4">
-      <c r="A295" s="8" t="s">
+      <c r="A295" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B295" s="8" t="s">
+      <c r="B295" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C295" s="8" t="s">
+      <c r="C295" s="14" t="s">
         <v>656</v>
       </c>
       <c r="D295" t="s">
@@ -8389,13 +8462,13 @@
       </c>
     </row>
     <row r="296" ht="14" customHeight="1" spans="1:4">
-      <c r="A296" s="8" t="s">
+      <c r="A296" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B296" s="8" t="s">
+      <c r="B296" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="C296" s="8" t="s">
+      <c r="C296" s="14" t="s">
         <v>658</v>
       </c>
       <c r="D296" t="s">
@@ -8403,13 +8476,13 @@
       </c>
     </row>
     <row r="297" ht="14" customHeight="1" spans="1:4">
-      <c r="A297" s="8" t="s">
+      <c r="A297" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B297" s="8" t="s">
+      <c r="B297" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C297" s="8" t="s">
+      <c r="C297" s="14" t="s">
         <v>661</v>
       </c>
       <c r="D297" t="s">
@@ -8417,13 +8490,13 @@
       </c>
     </row>
     <row r="298" ht="14" customHeight="1" spans="1:4">
-      <c r="A298" s="8" t="s">
+      <c r="A298" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B298" s="8" t="s">
+      <c r="B298" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C298" s="8" t="s">
+      <c r="C298" s="14" t="s">
         <v>663</v>
       </c>
       <c r="D298" t="s">
@@ -8431,13 +8504,13 @@
       </c>
     </row>
     <row r="299" ht="14" customHeight="1" spans="1:4">
-      <c r="A299" s="8" t="s">
+      <c r="A299" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B299" s="8" t="s">
+      <c r="B299" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C299" s="8" t="s">
+      <c r="C299" s="14" t="s">
         <v>665</v>
       </c>
       <c r="D299" t="s">
@@ -8445,13 +8518,13 @@
       </c>
     </row>
     <row r="300" ht="14" customHeight="1" spans="1:4">
-      <c r="A300" s="8" t="s">
+      <c r="A300" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B300" s="8" t="s">
+      <c r="B300" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C300" s="8" t="s">
+      <c r="C300" s="14" t="s">
         <v>667</v>
       </c>
       <c r="D300" t="s">
@@ -8459,13 +8532,13 @@
       </c>
     </row>
     <row r="301" ht="14" customHeight="1" spans="1:4">
-      <c r="A301" s="8" t="s">
+      <c r="A301" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="B301" s="8" t="s">
+      <c r="B301" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C301" s="8" t="s">
+      <c r="C301" s="14" t="s">
         <v>669</v>
       </c>
       <c r="D301" t="s">
@@ -8473,13 +8546,13 @@
       </c>
     </row>
     <row r="302" ht="14" customHeight="1" spans="1:4">
-      <c r="A302" s="8" t="s">
+      <c r="A302" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B302" s="8" t="s">
+      <c r="B302" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="C302" s="8" t="s">
+      <c r="C302" s="14" t="s">
         <v>673</v>
       </c>
       <c r="D302" t="s">
@@ -8487,13 +8560,13 @@
       </c>
     </row>
     <row r="303" ht="14" customHeight="1" spans="1:4">
-      <c r="A303" s="8" t="s">
+      <c r="A303" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B303" s="8" t="s">
+      <c r="B303" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="C303" s="8" t="s">
+      <c r="C303" s="14" t="s">
         <v>675</v>
       </c>
       <c r="D303" t="s">
@@ -8501,13 +8574,13 @@
       </c>
     </row>
     <row r="304" ht="14" customHeight="1" spans="1:4">
-      <c r="A304" s="8" t="s">
+      <c r="A304" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B304" s="8" t="s">
+      <c r="B304" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="C304" s="8" t="s">
+      <c r="C304" s="14" t="s">
         <v>677</v>
       </c>
       <c r="D304" t="s">
@@ -8515,13 +8588,13 @@
       </c>
     </row>
     <row r="305" ht="14" customHeight="1" spans="1:4">
-      <c r="A305" s="8" t="s">
+      <c r="A305" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B305" s="8" t="s">
+      <c r="B305" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="C305" s="8" t="s">
+      <c r="C305" s="14" t="s">
         <v>679</v>
       </c>
       <c r="D305" t="s">
@@ -8529,13 +8602,13 @@
       </c>
     </row>
     <row r="306" ht="14" customHeight="1" spans="1:4">
-      <c r="A306" s="8" t="s">
+      <c r="A306" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B306" s="8" t="s">
+      <c r="B306" s="14" t="s">
         <v>672</v>
       </c>
-      <c r="C306" s="8" t="s">
+      <c r="C306" s="14" t="s">
         <v>681</v>
       </c>
       <c r="D306" t="s">
@@ -8543,13 +8616,13 @@
       </c>
     </row>
     <row r="307" ht="14" customHeight="1" spans="1:4">
-      <c r="A307" s="8" t="s">
+      <c r="A307" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B307" s="8" t="s">
+      <c r="B307" s="14" t="s">
         <v>683</v>
       </c>
-      <c r="C307" s="8" t="s">
+      <c r="C307" s="14" t="s">
         <v>684</v>
       </c>
       <c r="D307" t="s">
@@ -8557,13 +8630,13 @@
       </c>
     </row>
     <row r="308" ht="14" customHeight="1" spans="1:4">
-      <c r="A308" s="8" t="s">
+      <c r="A308" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B308" s="8" t="s">
+      <c r="B308" s="14" t="s">
         <v>683</v>
       </c>
-      <c r="C308" s="8" t="s">
+      <c r="C308" s="14" t="s">
         <v>686</v>
       </c>
       <c r="D308" t="s">
@@ -8571,13 +8644,13 @@
       </c>
     </row>
     <row r="309" ht="14" customHeight="1" spans="1:4">
-      <c r="A309" s="8" t="s">
+      <c r="A309" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B309" s="8" t="s">
+      <c r="B309" s="14" t="s">
         <v>683</v>
       </c>
-      <c r="C309" s="8" t="s">
+      <c r="C309" s="14" t="s">
         <v>688</v>
       </c>
       <c r="D309" t="s">
@@ -8585,13 +8658,13 @@
       </c>
     </row>
     <row r="310" ht="14" customHeight="1" spans="1:4">
-      <c r="A310" s="8" t="s">
+      <c r="A310" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B310" s="8" t="s">
+      <c r="B310" s="14" t="s">
         <v>683</v>
       </c>
-      <c r="C310" s="8" t="s">
+      <c r="C310" s="14" t="s">
         <v>690</v>
       </c>
       <c r="D310" t="s">
@@ -8599,546 +8672,546 @@
       </c>
     </row>
     <row r="311" ht="14" customHeight="1" spans="1:4">
-      <c r="A311" s="8" t="s">
+      <c r="A311" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B311" s="8" t="s">
+      <c r="B311" s="14" t="s">
         <v>683</v>
       </c>
-      <c r="C311" s="8" t="s">
+      <c r="C311" s="14" t="s">
         <v>692</v>
       </c>
       <c r="D311" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="312" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A312" s="8" t="s">
+    <row r="312" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A312" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B312" s="8" t="s">
+      <c r="B312" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="C312" s="8" t="s">
+      <c r="C312" s="14" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="313" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A313" s="8" t="s">
+    <row r="313" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A313" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B313" s="8" t="s">
+      <c r="B313" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="C313" s="8" t="s">
+      <c r="C313" s="14" t="s">
         <v>696</v>
       </c>
     </row>
-    <row r="314" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A314" s="8" t="s">
+    <row r="314" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A314" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B314" s="8" t="s">
+      <c r="B314" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="C314" s="8" t="s">
+      <c r="C314" s="14" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="315" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A315" s="8" t="s">
+    <row r="315" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A315" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B315" s="8" t="s">
+      <c r="B315" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="C315" s="8" t="s">
+      <c r="C315" s="14" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="316" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A316" s="8" t="s">
+    <row r="316" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A316" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B316" s="8" t="s">
+      <c r="B316" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="C316" s="8" t="s">
+      <c r="C316" s="14" t="s">
         <v>701</v>
       </c>
-      <c r="D316" s="8"/>
-    </row>
-    <row r="317" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A317" s="8" t="s">
+      <c r="D316" s="14"/>
+    </row>
+    <row r="317" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A317" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="C317" s="8" t="s">
+      <c r="C317" s="14" t="s">
         <v>702</v>
       </c>
-      <c r="D317" s="8"/>
-    </row>
-    <row r="318" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A318" s="8" t="s">
+      <c r="D317" s="14"/>
+    </row>
+    <row r="318" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A318" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B318" s="8" t="s">
+      <c r="B318" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="C318" s="8" t="s">
+      <c r="C318" s="14" t="s">
         <v>703</v>
       </c>
-      <c r="D318" s="8"/>
-    </row>
-    <row r="319" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A319" s="8" t="s">
+      <c r="D318" s="14"/>
+    </row>
+    <row r="319" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A319" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B319" s="8" t="s">
+      <c r="B319" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="C319" s="8" t="s">
+      <c r="C319" s="14" t="s">
         <v>704</v>
       </c>
-      <c r="D319" s="8"/>
-    </row>
-    <row r="320" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A320" s="8" t="s">
+      <c r="D319" s="14"/>
+    </row>
+    <row r="320" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A320" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B320" s="8" t="s">
+      <c r="B320" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="C320" s="8" t="s">
+      <c r="C320" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="D320" s="8"/>
-    </row>
-    <row r="321" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A321" s="8" t="s">
+      <c r="D320" s="14"/>
+    </row>
+    <row r="321" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A321" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B321" s="8" t="s">
+      <c r="B321" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="C321" s="8" t="s">
+      <c r="C321" s="14" t="s">
         <v>707</v>
       </c>
-      <c r="D321" s="8"/>
-    </row>
-    <row r="322" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A322" s="8" t="s">
+      <c r="D321" s="14"/>
+    </row>
+    <row r="322" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A322" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B322" s="8" t="s">
+      <c r="B322" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="C322" s="8" t="s">
+      <c r="C322" s="14" t="s">
         <v>708</v>
       </c>
-      <c r="D322" s="8"/>
-    </row>
-    <row r="323" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A323" s="8" t="s">
+      <c r="D322" s="14"/>
+    </row>
+    <row r="323" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A323" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B323" s="8" t="s">
+      <c r="B323" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="C323" s="8" t="s">
+      <c r="C323" s="14" t="s">
         <v>709</v>
       </c>
-      <c r="D323" s="8"/>
-    </row>
-    <row r="324" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A324" s="8" t="s">
+      <c r="D323" s="14"/>
+    </row>
+    <row r="324" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A324" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B324" s="8" t="s">
+      <c r="B324" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="C324" s="8" t="s">
+      <c r="C324" s="14" t="s">
         <v>710</v>
       </c>
-      <c r="D324" s="8"/>
-    </row>
-    <row r="325" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A325" s="8" t="s">
+      <c r="D324" s="14"/>
+    </row>
+    <row r="325" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A325" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B325" s="8" t="s">
+      <c r="B325" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="C325" s="8" t="s">
+      <c r="C325" s="14" t="s">
         <v>712</v>
       </c>
-      <c r="D325" s="8"/>
-    </row>
-    <row r="326" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A326" s="8" t="s">
+      <c r="D325" s="14"/>
+    </row>
+    <row r="326" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A326" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B326" s="8" t="s">
+      <c r="B326" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="C326" s="8" t="s">
+      <c r="C326" s="14" t="s">
         <v>713</v>
       </c>
-      <c r="D326" s="8"/>
-    </row>
-    <row r="327" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A327" s="8" t="s">
+      <c r="D326" s="14"/>
+    </row>
+    <row r="327" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A327" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B327" s="8" t="s">
+      <c r="B327" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="C327" s="8" t="s">
+      <c r="C327" s="14" t="s">
         <v>714</v>
       </c>
-      <c r="D327" s="8"/>
-    </row>
-    <row r="328" s="9" customFormat="1" ht="14" customHeight="1" spans="1:4">
-      <c r="A328" s="8" t="s">
+      <c r="D327" s="14"/>
+    </row>
+    <row r="328" s="15" customFormat="1" ht="14" customHeight="1" spans="1:4">
+      <c r="A328" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="B328" s="8" t="s">
+      <c r="B328" s="14" t="s">
         <v>711</v>
       </c>
-      <c r="C328" s="8" t="s">
+      <c r="C328" s="14" t="s">
         <v>715</v>
       </c>
-      <c r="D328" s="8"/>
+      <c r="D328" s="14"/>
     </row>
     <row r="329" ht="14" customHeight="1" spans="1:4">
-      <c r="A329" s="8" t="s">
+      <c r="A329" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B329" s="8" t="s">
+      <c r="B329" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="C329" s="8" t="s">
+      <c r="C329" s="14" t="s">
         <v>717</v>
       </c>
     </row>
     <row r="330" ht="14" customHeight="1" spans="1:4">
-      <c r="A330" s="8" t="s">
+      <c r="A330" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B330" s="8" t="s">
+      <c r="B330" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="C330" s="8" t="s">
+      <c r="C330" s="14" t="s">
         <v>718</v>
       </c>
     </row>
     <row r="331" ht="14" customHeight="1" spans="1:4">
-      <c r="A331" s="8" t="s">
+      <c r="A331" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B331" s="8" t="s">
+      <c r="B331" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="C331" s="8" t="s">
+      <c r="C331" s="14" t="s">
         <v>719</v>
       </c>
     </row>
     <row r="332" ht="14" customHeight="1" spans="1:4">
-      <c r="A332" s="8" t="s">
+      <c r="A332" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B332" s="8" t="s">
+      <c r="B332" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="C332" s="8" t="s">
+      <c r="C332" s="14" t="s">
         <v>720</v>
       </c>
     </row>
     <row r="333" ht="14" customHeight="1" spans="1:4">
-      <c r="A333" s="8" t="s">
+      <c r="A333" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B333" s="8" t="s">
+      <c r="B333" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="C333" s="8" t="s">
+      <c r="C333" s="14" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="334" ht="14" customHeight="1" spans="1:4">
-      <c r="A334" s="8" t="s">
+      <c r="A334" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B334" s="8" t="s">
+      <c r="B334" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="C334" s="8" t="s">
+      <c r="C334" s="14" t="s">
         <v>723</v>
       </c>
     </row>
     <row r="335" ht="14" customHeight="1" spans="1:4">
-      <c r="A335" s="8" t="s">
+      <c r="A335" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B335" s="8" t="s">
+      <c r="B335" s="14" t="s">
         <v>721</v>
       </c>
-      <c r="C335" s="8" t="s">
+      <c r="C335" s="14" t="s">
         <v>724</v>
       </c>
     </row>
     <row r="336" ht="14" customHeight="1" spans="1:4">
-      <c r="A336" s="8" t="s">
+      <c r="A336" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B336" s="8" t="s">
+      <c r="B336" s="14" t="s">
         <v>725</v>
       </c>
-      <c r="C336" s="8" t="s">
+      <c r="C336" s="14" t="s">
         <v>726</v>
       </c>
     </row>
     <row r="337" ht="14" customHeight="1" spans="1:3">
-      <c r="A337" s="8" t="s">
+      <c r="A337" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B337" s="8" t="s">
+      <c r="B337" s="14" t="s">
         <v>725</v>
       </c>
-      <c r="C337" s="8" t="s">
+      <c r="C337" s="14" t="s">
         <v>727</v>
       </c>
     </row>
     <row r="338" ht="14" customHeight="1" spans="1:3">
-      <c r="A338" s="8" t="s">
+      <c r="A338" s="14" t="s">
         <v>716</v>
       </c>
-      <c r="B338" s="8" t="s">
+      <c r="B338" s="14" t="s">
         <v>725</v>
       </c>
-      <c r="C338" s="8" t="s">
+      <c r="C338" s="14" t="s">
         <v>728</v>
       </c>
     </row>
     <row r="339" ht="14" customHeight="1" spans="1:3">
-      <c r="A339" s="8" t="s">
+      <c r="A339" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B339" s="8" t="s">
+      <c r="B339" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C339" s="8" t="s">
+      <c r="C339" s="14" t="s">
         <v>731</v>
       </c>
     </row>
     <row r="340" ht="14" customHeight="1" spans="1:3">
-      <c r="A340" s="8" t="s">
+      <c r="A340" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B340" s="8" t="s">
+      <c r="B340" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C340" s="8" t="s">
+      <c r="C340" s="14" t="s">
         <v>732</v>
       </c>
     </row>
     <row r="341" ht="14" customHeight="1" spans="1:3">
-      <c r="A341" s="8" t="s">
+      <c r="A341" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B341" s="8" t="s">
+      <c r="B341" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C341" s="8" t="s">
+      <c r="C341" s="14" t="s">
         <v>733</v>
       </c>
     </row>
     <row r="342" ht="14" customHeight="1" spans="1:3">
-      <c r="A342" s="8" t="s">
+      <c r="A342" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B342" s="8" t="s">
+      <c r="B342" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C342" s="8" t="s">
+      <c r="C342" s="14" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="343" ht="14" customHeight="1" spans="1:3">
-      <c r="A343" s="8" t="s">
+      <c r="A343" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B343" s="8" t="s">
+      <c r="B343" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C343" s="8" t="s">
+      <c r="C343" s="14" t="s">
         <v>735</v>
       </c>
     </row>
     <row r="344" ht="14" customHeight="1" spans="1:3">
-      <c r="A344" s="8" t="s">
+      <c r="A344" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B344" s="8" t="s">
+      <c r="B344" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C344" s="8" t="s">
+      <c r="C344" s="14" t="s">
         <v>736</v>
       </c>
     </row>
     <row r="345" ht="14" customHeight="1" spans="1:3">
-      <c r="A345" s="8" t="s">
+      <c r="A345" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B345" s="8" t="s">
+      <c r="B345" s="14" t="s">
         <v>730</v>
       </c>
-      <c r="C345" s="8" t="s">
+      <c r="C345" s="14" t="s">
         <v>737</v>
       </c>
     </row>
     <row r="346" ht="14" customHeight="1" spans="1:3">
-      <c r="A346" s="8" t="s">
+      <c r="A346" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B346" s="8" t="s">
+      <c r="B346" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C346" s="8" t="s">
+      <c r="C346" s="14" t="s">
         <v>739</v>
       </c>
     </row>
     <row r="347" ht="14" customHeight="1" spans="1:3">
-      <c r="A347" s="8" t="s">
+      <c r="A347" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B347" s="8" t="s">
+      <c r="B347" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C347" s="8" t="s">
+      <c r="C347" s="14" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="348" ht="14" customHeight="1" spans="1:3">
-      <c r="A348" s="8" t="s">
+      <c r="A348" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B348" s="8" t="s">
+      <c r="B348" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C348" s="8" t="s">
+      <c r="C348" s="14" t="s">
         <v>741</v>
       </c>
     </row>
     <row r="349" ht="14" customHeight="1" spans="1:3">
-      <c r="A349" s="8" t="s">
+      <c r="A349" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B349" s="8" t="s">
+      <c r="B349" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C349" s="8" t="s">
+      <c r="C349" s="14" t="s">
         <v>742</v>
       </c>
     </row>
     <row r="350" ht="14" customHeight="1" spans="1:3">
-      <c r="A350" s="8" t="s">
+      <c r="A350" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B350" s="8" t="s">
+      <c r="B350" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C350" s="8" t="s">
+      <c r="C350" s="14" t="s">
         <v>743</v>
       </c>
     </row>
     <row r="351" ht="14" customHeight="1" spans="1:3">
-      <c r="A351" s="8" t="s">
+      <c r="A351" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B351" s="8" t="s">
+      <c r="B351" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C351" s="8" t="s">
+      <c r="C351" s="14" t="s">
         <v>744</v>
       </c>
     </row>
     <row r="352" ht="14" customHeight="1" spans="1:3">
-      <c r="A352" s="8" t="s">
+      <c r="A352" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B352" s="8" t="s">
+      <c r="B352" s="14" t="s">
         <v>738</v>
       </c>
-      <c r="C352" s="8" t="s">
+      <c r="C352" s="14" t="s">
         <v>745</v>
       </c>
     </row>
     <row r="353" ht="14" customHeight="1" spans="1:4">
-      <c r="A353" s="8" t="s">
+      <c r="A353" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B353" s="8" t="s">
+      <c r="B353" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="C353" s="8" t="s">
+      <c r="C353" s="14" t="s">
         <v>747</v>
       </c>
     </row>
     <row r="354" ht="14" customHeight="1" spans="1:4">
-      <c r="A354" s="8" t="s">
+      <c r="A354" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B354" s="8" t="s">
+      <c r="B354" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="C354" s="8" t="s">
+      <c r="C354" s="14" t="s">
         <v>748</v>
       </c>
     </row>
     <row r="355" ht="14" customHeight="1" spans="1:4">
-      <c r="A355" s="8" t="s">
+      <c r="A355" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B355" s="8" t="s">
+      <c r="B355" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="C355" s="8" t="s">
+      <c r="C355" s="14" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="356" ht="14" customHeight="1" spans="1:4">
-      <c r="A356" s="8" t="s">
+      <c r="A356" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B356" s="8" t="s">
+      <c r="B356" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="C356" s="8" t="s">
+      <c r="C356" s="14" t="s">
         <v>750</v>
       </c>
     </row>
     <row r="357" ht="14" customHeight="1" spans="1:4">
-      <c r="A357" s="8" t="s">
+      <c r="A357" s="14" t="s">
         <v>729</v>
       </c>
-      <c r="B357" s="8" t="s">
+      <c r="B357" s="14" t="s">
         <v>746</v>
       </c>
-      <c r="C357" s="8" t="s">
+      <c r="C357" s="14" t="s">
         <v>751</v>
       </c>
     </row>
     <row r="358" spans="1:4">
-      <c r="A358" s="8" t="s">
+      <c r="A358" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B358" s="8" t="s">
+      <c r="B358" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C358" s="8" t="s">
+      <c r="C358" s="14" t="s">
         <v>754</v>
       </c>
       <c r="D358" t="s">
@@ -9146,13 +9219,13 @@
       </c>
     </row>
     <row r="359" spans="1:4">
-      <c r="A359" s="8" t="s">
+      <c r="A359" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B359" s="8" t="s">
+      <c r="B359" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C359" s="8" t="s">
+      <c r="C359" s="14" t="s">
         <v>756</v>
       </c>
       <c r="D359" t="s">
@@ -9160,13 +9233,13 @@
       </c>
     </row>
     <row r="360" spans="1:4">
-      <c r="A360" s="8" t="s">
+      <c r="A360" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B360" s="8" t="s">
+      <c r="B360" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C360" s="8" t="s">
+      <c r="C360" s="14" t="s">
         <v>758</v>
       </c>
       <c r="D360" t="s">
@@ -9174,13 +9247,13 @@
       </c>
     </row>
     <row r="361" spans="1:4">
-      <c r="A361" s="8" t="s">
+      <c r="A361" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B361" s="8" t="s">
+      <c r="B361" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C361" s="8" t="s">
+      <c r="C361" s="14" t="s">
         <v>760</v>
       </c>
       <c r="D361" t="s">
@@ -9188,13 +9261,13 @@
       </c>
     </row>
     <row r="362" spans="1:4">
-      <c r="A362" s="8" t="s">
+      <c r="A362" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B362" s="8" t="s">
+      <c r="B362" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C362" s="8" t="s">
+      <c r="C362" s="14" t="s">
         <v>762</v>
       </c>
       <c r="D362" t="s">
@@ -9202,13 +9275,13 @@
       </c>
     </row>
     <row r="363" spans="1:4">
-      <c r="A363" s="8" t="s">
+      <c r="A363" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B363" s="8" t="s">
+      <c r="B363" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C363" s="8" t="s">
+      <c r="C363" s="14" t="s">
         <v>764</v>
       </c>
       <c r="D363" t="s">
@@ -9216,13 +9289,13 @@
       </c>
     </row>
     <row r="364" spans="1:4">
-      <c r="A364" s="8" t="s">
+      <c r="A364" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B364" s="8" t="s">
+      <c r="B364" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C364" s="8" t="s">
+      <c r="C364" s="14" t="s">
         <v>766</v>
       </c>
       <c r="D364" t="s">
@@ -9230,13 +9303,13 @@
       </c>
     </row>
     <row r="365" spans="1:4">
-      <c r="A365" s="8" t="s">
+      <c r="A365" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B365" s="8" t="s">
+      <c r="B365" s="14" t="s">
         <v>753</v>
       </c>
-      <c r="C365" s="8" t="s">
+      <c r="C365" s="14" t="s">
         <v>768</v>
       </c>
       <c r="D365" t="s">
@@ -9244,13 +9317,13 @@
       </c>
     </row>
     <row r="366" spans="1:4">
-      <c r="A366" s="8" t="s">
+      <c r="A366" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B366" s="8" t="s">
+      <c r="B366" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C366" s="8" t="s">
+      <c r="C366" s="14" t="s">
         <v>771</v>
       </c>
       <c r="D366" t="s">
@@ -9258,13 +9331,13 @@
       </c>
     </row>
     <row r="367" spans="1:4">
-      <c r="A367" s="8" t="s">
+      <c r="A367" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B367" s="8" t="s">
+      <c r="B367" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C367" s="8" t="s">
+      <c r="C367" s="14" t="s">
         <v>773</v>
       </c>
       <c r="D367" t="s">
@@ -9272,13 +9345,13 @@
       </c>
     </row>
     <row r="368" spans="1:4">
-      <c r="A368" s="8" t="s">
+      <c r="A368" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B368" s="8" t="s">
+      <c r="B368" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C368" s="8" t="s">
+      <c r="C368" s="14" t="s">
         <v>775</v>
       </c>
       <c r="D368" t="s">
@@ -9286,13 +9359,13 @@
       </c>
     </row>
     <row r="369" spans="1:4">
-      <c r="A369" s="8" t="s">
+      <c r="A369" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B369" s="8" t="s">
+      <c r="B369" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C369" s="8" t="s">
+      <c r="C369" s="14" t="s">
         <v>777</v>
       </c>
       <c r="D369" t="s">
@@ -9300,13 +9373,13 @@
       </c>
     </row>
     <row r="370" spans="1:4">
-      <c r="A370" s="8" t="s">
+      <c r="A370" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B370" s="8" t="s">
+      <c r="B370" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C370" s="8" t="s">
+      <c r="C370" s="14" t="s">
         <v>779</v>
       </c>
       <c r="D370" t="s">
@@ -9314,13 +9387,13 @@
       </c>
     </row>
     <row r="371" spans="1:4">
-      <c r="A371" s="8" t="s">
+      <c r="A371" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B371" s="8" t="s">
+      <c r="B371" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C371" s="8" t="s">
+      <c r="C371" s="14" t="s">
         <v>781</v>
       </c>
       <c r="D371" t="s">
@@ -9328,13 +9401,13 @@
       </c>
     </row>
     <row r="372" spans="1:4">
-      <c r="A372" s="8" t="s">
+      <c r="A372" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B372" s="8" t="s">
+      <c r="B372" s="14" t="s">
         <v>770</v>
       </c>
-      <c r="C372" s="8" t="s">
+      <c r="C372" s="14" t="s">
         <v>783</v>
       </c>
       <c r="D372" t="s">
@@ -9342,13 +9415,13 @@
       </c>
     </row>
     <row r="373" spans="1:4">
-      <c r="A373" s="8" t="s">
+      <c r="A373" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B373" s="8" t="s">
+      <c r="B373" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C373" s="8" t="s">
+      <c r="C373" s="14" t="s">
         <v>786</v>
       </c>
       <c r="D373" t="s">
@@ -9356,13 +9429,13 @@
       </c>
     </row>
     <row r="374" spans="1:4">
-      <c r="A374" s="8" t="s">
+      <c r="A374" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B374" s="8" t="s">
+      <c r="B374" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C374" s="8" t="s">
+      <c r="C374" s="14" t="s">
         <v>788</v>
       </c>
       <c r="D374" t="s">
@@ -9370,13 +9443,13 @@
       </c>
     </row>
     <row r="375" spans="1:4">
-      <c r="A375" s="8" t="s">
+      <c r="A375" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B375" s="8" t="s">
+      <c r="B375" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C375" s="8" t="s">
+      <c r="C375" s="14" t="s">
         <v>790</v>
       </c>
       <c r="D375" t="s">
@@ -9384,13 +9457,13 @@
       </c>
     </row>
     <row r="376" spans="1:4">
-      <c r="A376" s="8" t="s">
+      <c r="A376" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B376" s="8" t="s">
+      <c r="B376" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C376" s="8" t="s">
+      <c r="C376" s="14" t="s">
         <v>792</v>
       </c>
       <c r="D376" t="s">
@@ -9398,13 +9471,13 @@
       </c>
     </row>
     <row r="377" spans="1:4">
-      <c r="A377" s="8" t="s">
+      <c r="A377" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B377" s="8" t="s">
+      <c r="B377" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C377" s="8" t="s">
+      <c r="C377" s="14" t="s">
         <v>794</v>
       </c>
       <c r="D377" t="s">
@@ -9412,13 +9485,13 @@
       </c>
     </row>
     <row r="378" spans="1:4">
-      <c r="A378" s="8" t="s">
+      <c r="A378" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B378" s="8" t="s">
+      <c r="B378" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C378" s="8" t="s">
+      <c r="C378" s="14" t="s">
         <v>796</v>
       </c>
       <c r="D378" t="s">
@@ -9426,13 +9499,13 @@
       </c>
     </row>
     <row r="379" spans="1:4">
-      <c r="A379" s="8" t="s">
+      <c r="A379" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B379" s="8" t="s">
+      <c r="B379" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C379" s="8" t="s">
+      <c r="C379" s="14" t="s">
         <v>798</v>
       </c>
       <c r="D379" t="s">
@@ -9440,13 +9513,13 @@
       </c>
     </row>
     <row r="380" spans="1:4">
-      <c r="A380" s="8" t="s">
+      <c r="A380" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B380" s="8" t="s">
+      <c r="B380" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C380" s="8" t="s">
+      <c r="C380" s="14" t="s">
         <v>800</v>
       </c>
       <c r="D380" t="s">
@@ -9454,13 +9527,13 @@
       </c>
     </row>
     <row r="381" spans="1:4">
-      <c r="A381" s="8" t="s">
+      <c r="A381" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B381" s="8" t="s">
+      <c r="B381" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C381" s="8" t="s">
+      <c r="C381" s="14" t="s">
         <v>802</v>
       </c>
       <c r="D381" t="s">
@@ -9468,13 +9541,13 @@
       </c>
     </row>
     <row r="382" spans="1:4">
-      <c r="A382" s="8" t="s">
+      <c r="A382" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B382" s="8" t="s">
+      <c r="B382" s="14" t="s">
         <v>785</v>
       </c>
-      <c r="C382" s="8" t="s">
+      <c r="C382" s="14" t="s">
         <v>804</v>
       </c>
       <c r="D382" t="s">
@@ -9482,13 +9555,13 @@
       </c>
     </row>
     <row r="383" spans="1:4">
-      <c r="A383" s="8" t="s">
+      <c r="A383" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B383" s="8" t="s">
+      <c r="B383" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C383" s="8" t="s">
+      <c r="C383" s="14" t="s">
         <v>807</v>
       </c>
       <c r="D383" t="s">
@@ -9496,13 +9569,13 @@
       </c>
     </row>
     <row r="384" spans="1:4">
-      <c r="A384" s="8" t="s">
+      <c r="A384" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B384" s="8" t="s">
+      <c r="B384" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C384" s="8" t="s">
+      <c r="C384" s="14" t="s">
         <v>809</v>
       </c>
       <c r="D384" t="s">
@@ -9510,13 +9583,13 @@
       </c>
     </row>
     <row r="385" spans="1:4">
-      <c r="A385" s="8" t="s">
+      <c r="A385" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B385" s="8" t="s">
+      <c r="B385" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C385" s="8" t="s">
+      <c r="C385" s="14" t="s">
         <v>811</v>
       </c>
       <c r="D385" t="s">
@@ -9524,13 +9597,13 @@
       </c>
     </row>
     <row r="386" spans="1:4">
-      <c r="A386" s="8" t="s">
+      <c r="A386" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B386" s="8" t="s">
+      <c r="B386" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C386" s="8" t="s">
+      <c r="C386" s="14" t="s">
         <v>812</v>
       </c>
       <c r="D386" t="s">
@@ -9538,13 +9611,13 @@
       </c>
     </row>
     <row r="387" spans="1:4">
-      <c r="A387" s="8" t="s">
+      <c r="A387" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B387" s="8" t="s">
+      <c r="B387" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C387" s="8" t="s">
+      <c r="C387" s="14" t="s">
         <v>814</v>
       </c>
       <c r="D387" t="s">
@@ -9552,13 +9625,13 @@
       </c>
     </row>
     <row r="388" spans="1:4">
-      <c r="A388" s="8" t="s">
+      <c r="A388" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B388" s="8" t="s">
+      <c r="B388" s="14" t="s">
         <v>806</v>
       </c>
-      <c r="C388" s="8" t="s">
+      <c r="C388" s="14" t="s">
         <v>816</v>
       </c>
       <c r="D388" t="s">
@@ -9566,13 +9639,13 @@
       </c>
     </row>
     <row r="389" spans="1:4">
-      <c r="A389" s="8" t="s">
+      <c r="A389" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B389" s="8" t="s">
+      <c r="B389" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C389" s="8" t="s">
+      <c r="C389" s="14" t="s">
         <v>819</v>
       </c>
       <c r="D389" t="s">
@@ -9580,13 +9653,13 @@
       </c>
     </row>
     <row r="390" spans="1:4">
-      <c r="A390" s="8" t="s">
+      <c r="A390" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B390" s="8" t="s">
+      <c r="B390" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C390" s="8" t="s">
+      <c r="C390" s="14" t="s">
         <v>821</v>
       </c>
       <c r="D390" t="s">
@@ -9594,13 +9667,13 @@
       </c>
     </row>
     <row r="391" spans="1:4">
-      <c r="A391" s="8" t="s">
+      <c r="A391" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B391" s="8" t="s">
+      <c r="B391" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C391" s="8" t="s">
+      <c r="C391" s="14" t="s">
         <v>823</v>
       </c>
       <c r="D391" t="s">
@@ -9608,13 +9681,13 @@
       </c>
     </row>
     <row r="392" spans="1:4">
-      <c r="A392" s="8" t="s">
+      <c r="A392" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B392" s="8" t="s">
+      <c r="B392" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C392" s="8" t="s">
+      <c r="C392" s="14" t="s">
         <v>825</v>
       </c>
       <c r="D392" t="s">
@@ -9622,13 +9695,13 @@
       </c>
     </row>
     <row r="393" spans="1:4">
-      <c r="A393" s="8" t="s">
+      <c r="A393" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B393" s="8" t="s">
+      <c r="B393" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C393" s="8" t="s">
+      <c r="C393" s="14" t="s">
         <v>827</v>
       </c>
       <c r="D393" t="s">
@@ -9636,13 +9709,13 @@
       </c>
     </row>
     <row r="394" spans="1:4">
-      <c r="A394" s="8" t="s">
+      <c r="A394" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B394" s="8" t="s">
+      <c r="B394" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C394" s="8" t="s">
+      <c r="C394" s="14" t="s">
         <v>829</v>
       </c>
       <c r="D394" t="s">
@@ -9650,13 +9723,13 @@
       </c>
     </row>
     <row r="395" spans="1:4">
-      <c r="A395" s="8" t="s">
+      <c r="A395" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B395" s="8" t="s">
+      <c r="B395" s="14" t="s">
         <v>818</v>
       </c>
-      <c r="C395" s="8" t="s">
+      <c r="C395" s="14" t="s">
         <v>831</v>
       </c>
       <c r="D395" t="s">
@@ -9664,13 +9737,13 @@
       </c>
     </row>
     <row r="396" spans="1:4">
-      <c r="A396" s="8" t="s">
+      <c r="A396" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B396" s="8" t="s">
+      <c r="B396" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C396" s="8" t="s">
+      <c r="C396" s="14" t="s">
         <v>834</v>
       </c>
       <c r="D396" t="s">
@@ -9678,13 +9751,13 @@
       </c>
     </row>
     <row r="397" spans="1:4">
-      <c r="A397" s="8" t="s">
+      <c r="A397" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B397" s="8" t="s">
+      <c r="B397" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C397" s="8" t="s">
+      <c r="C397" s="14" t="s">
         <v>836</v>
       </c>
       <c r="D397" t="s">
@@ -9692,13 +9765,13 @@
       </c>
     </row>
     <row r="398" spans="1:4">
-      <c r="A398" s="8" t="s">
+      <c r="A398" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B398" s="8" t="s">
+      <c r="B398" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C398" s="8" t="s">
+      <c r="C398" s="14" t="s">
         <v>838</v>
       </c>
       <c r="D398" t="s">
@@ -9706,13 +9779,13 @@
       </c>
     </row>
     <row r="399" spans="1:4">
-      <c r="A399" s="8" t="s">
+      <c r="A399" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B399" s="8" t="s">
+      <c r="B399" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C399" s="8" t="s">
+      <c r="C399" s="14" t="s">
         <v>840</v>
       </c>
       <c r="D399" t="s">
@@ -9720,13 +9793,13 @@
       </c>
     </row>
     <row r="400" spans="1:4">
-      <c r="A400" s="8" t="s">
+      <c r="A400" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B400" s="8" t="s">
+      <c r="B400" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C400" s="8" t="s">
+      <c r="C400" s="14" t="s">
         <v>842</v>
       </c>
       <c r="D400" t="s">
@@ -9734,13 +9807,13 @@
       </c>
     </row>
     <row r="401" spans="1:4">
-      <c r="A401" s="8" t="s">
+      <c r="A401" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B401" s="8" t="s">
+      <c r="B401" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C401" s="8" t="s">
+      <c r="C401" s="14" t="s">
         <v>844</v>
       </c>
       <c r="D401" t="s">
@@ -9748,13 +9821,13 @@
       </c>
     </row>
     <row r="402" spans="1:4">
-      <c r="A402" s="8" t="s">
+      <c r="A402" s="14" t="s">
         <v>752</v>
       </c>
-      <c r="B402" s="8" t="s">
+      <c r="B402" s="14" t="s">
         <v>833</v>
       </c>
-      <c r="C402" s="8" t="s">
+      <c r="C402" s="14" t="s">
         <v>846</v>
       </c>
       <c r="D402" t="s">
@@ -9762,13 +9835,13 @@
       </c>
     </row>
     <row r="403" spans="1:4">
-      <c r="A403" s="8" t="s">
+      <c r="A403" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B403" s="8" t="s">
+      <c r="B403" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C403" s="8" t="s">
+      <c r="C403" s="14" t="s">
         <v>850</v>
       </c>
       <c r="D403" t="s">
@@ -9776,13 +9849,13 @@
       </c>
     </row>
     <row r="404" spans="1:4">
-      <c r="A404" s="8" t="s">
+      <c r="A404" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B404" s="8" t="s">
+      <c r="B404" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C404" s="8" t="s">
+      <c r="C404" s="14" t="s">
         <v>852</v>
       </c>
       <c r="D404" t="s">
@@ -9790,13 +9863,13 @@
       </c>
     </row>
     <row r="405" spans="1:4">
-      <c r="A405" s="8" t="s">
+      <c r="A405" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B405" s="8" t="s">
+      <c r="B405" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C405" s="8" t="s">
+      <c r="C405" s="14" t="s">
         <v>854</v>
       </c>
       <c r="D405" t="s">
@@ -9804,13 +9877,13 @@
       </c>
     </row>
     <row r="406" spans="1:4">
-      <c r="A406" s="8" t="s">
+      <c r="A406" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B406" s="8" t="s">
+      <c r="B406" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C406" s="8" t="s">
+      <c r="C406" s="14" t="s">
         <v>856</v>
       </c>
       <c r="D406" t="s">
@@ -9818,13 +9891,13 @@
       </c>
     </row>
     <row r="407" spans="1:4">
-      <c r="A407" s="8" t="s">
+      <c r="A407" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B407" s="8" t="s">
+      <c r="B407" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C407" s="8" t="s">
+      <c r="C407" s="14" t="s">
         <v>858</v>
       </c>
       <c r="D407" t="s">
@@ -9832,13 +9905,13 @@
       </c>
     </row>
     <row r="408" spans="1:4">
-      <c r="A408" s="8" t="s">
+      <c r="A408" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B408" s="8" t="s">
+      <c r="B408" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C408" s="8" t="s">
+      <c r="C408" s="14" t="s">
         <v>860</v>
       </c>
       <c r="D408" t="s">
@@ -9846,13 +9919,13 @@
       </c>
     </row>
     <row r="409" spans="1:4">
-      <c r="A409" s="8" t="s">
+      <c r="A409" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B409" s="8" t="s">
+      <c r="B409" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C409" s="8" t="s">
+      <c r="C409" s="14" t="s">
         <v>862</v>
       </c>
       <c r="D409" t="s">
@@ -9860,13 +9933,13 @@
       </c>
     </row>
     <row r="410" spans="1:4">
-      <c r="A410" s="8" t="s">
+      <c r="A410" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B410" s="8" t="s">
+      <c r="B410" s="14" t="s">
         <v>849</v>
       </c>
-      <c r="C410" s="8" t="s">
+      <c r="C410" s="14" t="s">
         <v>864</v>
       </c>
       <c r="D410" t="s">
@@ -9874,13 +9947,13 @@
       </c>
     </row>
     <row r="411" spans="1:4">
-      <c r="A411" s="8" t="s">
+      <c r="A411" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B411" s="8" t="s">
+      <c r="B411" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C411" s="8" t="s">
+      <c r="C411" s="14" t="s">
         <v>867</v>
       </c>
       <c r="D411" t="s">
@@ -9888,13 +9961,13 @@
       </c>
     </row>
     <row r="412" spans="1:4">
-      <c r="A412" s="8" t="s">
+      <c r="A412" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B412" s="8" t="s">
+      <c r="B412" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C412" s="8" t="s">
+      <c r="C412" s="14" t="s">
         <v>869</v>
       </c>
       <c r="D412" t="s">
@@ -9902,13 +9975,13 @@
       </c>
     </row>
     <row r="413" spans="1:4">
-      <c r="A413" s="8" t="s">
+      <c r="A413" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B413" s="8" t="s">
+      <c r="B413" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C413" s="8" t="s">
+      <c r="C413" s="14" t="s">
         <v>871</v>
       </c>
       <c r="D413" t="s">
@@ -9916,13 +9989,13 @@
       </c>
     </row>
     <row r="414" spans="1:4">
-      <c r="A414" s="8" t="s">
+      <c r="A414" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B414" s="8" t="s">
+      <c r="B414" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C414" s="8" t="s">
+      <c r="C414" s="14" t="s">
         <v>873</v>
       </c>
       <c r="D414" t="s">
@@ -9930,13 +10003,13 @@
       </c>
     </row>
     <row r="415" spans="1:4">
-      <c r="A415" s="8" t="s">
+      <c r="A415" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B415" s="8" t="s">
+      <c r="B415" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C415" s="8" t="s">
+      <c r="C415" s="14" t="s">
         <v>875</v>
       </c>
       <c r="D415" t="s">
@@ -9944,13 +10017,13 @@
       </c>
     </row>
     <row r="416" spans="1:4">
-      <c r="A416" s="8" t="s">
+      <c r="A416" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B416" s="8" t="s">
+      <c r="B416" s="14" t="s">
         <v>866</v>
       </c>
-      <c r="C416" s="8" t="s">
+      <c r="C416" s="14" t="s">
         <v>877</v>
       </c>
       <c r="D416" t="s">
@@ -9958,13 +10031,13 @@
       </c>
     </row>
     <row r="417" spans="1:5">
-      <c r="A417" s="8" t="s">
+      <c r="A417" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B417" s="8" t="s">
+      <c r="B417" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C417" s="8" t="s">
+      <c r="C417" s="14" t="s">
         <v>880</v>
       </c>
       <c r="D417" t="s">
@@ -9972,13 +10045,13 @@
       </c>
     </row>
     <row r="418" spans="1:5">
-      <c r="A418" s="8" t="s">
+      <c r="A418" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B418" s="8" t="s">
+      <c r="B418" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C418" s="8" t="s">
+      <c r="C418" s="14" t="s">
         <v>882</v>
       </c>
       <c r="D418" t="s">
@@ -9986,13 +10059,13 @@
       </c>
     </row>
     <row r="419" spans="1:5">
-      <c r="A419" s="8" t="s">
+      <c r="A419" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B419" s="8" t="s">
+      <c r="B419" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C419" s="8" t="s">
+      <c r="C419" s="14" t="s">
         <v>884</v>
       </c>
       <c r="D419" t="s">
@@ -10000,13 +10073,13 @@
       </c>
     </row>
     <row r="420" spans="1:5">
-      <c r="A420" s="8" t="s">
+      <c r="A420" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B420" s="8" t="s">
+      <c r="B420" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C420" s="8" t="s">
+      <c r="C420" s="14" t="s">
         <v>886</v>
       </c>
       <c r="D420" t="s">
@@ -10014,13 +10087,13 @@
       </c>
     </row>
     <row r="421" spans="1:5">
-      <c r="A421" s="8" t="s">
+      <c r="A421" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B421" s="8" t="s">
+      <c r="B421" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C421" s="8" t="s">
+      <c r="C421" s="14" t="s">
         <v>888</v>
       </c>
       <c r="D421" t="s">
@@ -10028,13 +10101,13 @@
       </c>
     </row>
     <row r="422" spans="1:5">
-      <c r="A422" s="8" t="s">
+      <c r="A422" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B422" s="8" t="s">
+      <c r="B422" s="14" t="s">
         <v>879</v>
       </c>
-      <c r="C422" s="8" t="s">
+      <c r="C422" s="14" t="s">
         <v>890</v>
       </c>
       <c r="D422" t="s">
@@ -10042,13 +10115,13 @@
       </c>
     </row>
     <row r="423" spans="1:5">
-      <c r="A423" s="8" t="s">
+      <c r="A423" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B423" s="8" t="s">
+      <c r="B423" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C423" s="8" t="s">
+      <c r="C423" s="14" t="s">
         <v>893</v>
       </c>
       <c r="D423" t="s">
@@ -10056,13 +10129,13 @@
       </c>
     </row>
     <row r="424" spans="1:5">
-      <c r="A424" s="8" t="s">
+      <c r="A424" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B424" s="8" t="s">
+      <c r="B424" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C424" s="8" t="s">
+      <c r="C424" s="14" t="s">
         <v>895</v>
       </c>
       <c r="D424" t="s">
@@ -10070,13 +10143,13 @@
       </c>
     </row>
     <row r="425" spans="1:5">
-      <c r="A425" s="8" t="s">
+      <c r="A425" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B425" s="8" t="s">
+      <c r="B425" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C425" s="8" t="s">
+      <c r="C425" s="14" t="s">
         <v>897</v>
       </c>
       <c r="D425" t="s">
@@ -10084,13 +10157,13 @@
       </c>
     </row>
     <row r="426" spans="1:5">
-      <c r="A426" s="8" t="s">
+      <c r="A426" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B426" s="8" t="s">
+      <c r="B426" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C426" s="8" t="s">
+      <c r="C426" s="14" t="s">
         <v>899</v>
       </c>
       <c r="D426" t="s">
@@ -10098,13 +10171,13 @@
       </c>
     </row>
     <row r="427" spans="1:5">
-      <c r="A427" s="8" t="s">
+      <c r="A427" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B427" s="8" t="s">
+      <c r="B427" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C427" s="8" t="s">
+      <c r="C427" s="14" t="s">
         <v>901</v>
       </c>
       <c r="D427" t="s">
@@ -10112,13 +10185,13 @@
       </c>
     </row>
     <row r="428" spans="1:5">
-      <c r="A428" s="8" t="s">
+      <c r="A428" s="14" t="s">
         <v>848</v>
       </c>
-      <c r="B428" s="8" t="s">
+      <c r="B428" s="14" t="s">
         <v>892</v>
       </c>
-      <c r="C428" s="8" t="s">
+      <c r="C428" s="14" t="s">
         <v>903</v>
       </c>
       <c r="D428" t="s">
@@ -10126,57 +10199,57 @@
       </c>
     </row>
     <row r="429" spans="1:5">
-      <c r="A429" s="8" t="s">
+      <c r="A429" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B429" s="8" t="s">
+      <c r="B429" s="14" t="s">
         <v>906</v>
       </c>
-      <c r="C429" s="8" t="s">
+      <c r="C429" s="14" t="s">
         <v>907</v>
       </c>
-      <c r="D429" s="11" t="s">
+      <c r="D429" s="17" t="s">
         <v>908</v>
       </c>
     </row>
     <row r="430" spans="1:5">
-      <c r="A430" s="8" t="s">
+      <c r="A430" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B430" s="8" t="s">
+      <c r="B430" s="14" t="s">
         <v>906</v>
       </c>
-      <c r="C430" s="8" t="s">
+      <c r="C430" s="14" t="s">
         <v>909</v>
       </c>
-      <c r="D430" s="11" t="s">
+      <c r="D430" s="17" t="s">
         <v>910</v>
       </c>
-      <c r="E430" s="8"/>
+      <c r="E430" s="14"/>
     </row>
     <row r="431" spans="1:5">
-      <c r="A431" s="8" t="s">
+      <c r="A431" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B431" s="8" t="s">
+      <c r="B431" s="14" t="s">
         <v>906</v>
       </c>
-      <c r="C431" s="8" t="s">
+      <c r="C431" s="14" t="s">
         <v>911</v>
       </c>
-      <c r="D431" s="11" t="s">
+      <c r="D431" s="17" t="s">
         <v>912</v>
       </c>
-      <c r="E431" s="8"/>
+      <c r="E431" s="14"/>
     </row>
     <row r="432" spans="1:5">
-      <c r="A432" s="8" t="s">
+      <c r="A432" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B432" s="8" t="s">
+      <c r="B432" s="14" t="s">
         <v>906</v>
       </c>
-      <c r="C432" s="8" t="s">
+      <c r="C432" s="14" t="s">
         <v>913</v>
       </c>
       <c r="D432" t="s">
@@ -10184,270 +10257,270 @@
       </c>
     </row>
     <row r="433" spans="1:4">
-      <c r="A433" s="8" t="s">
+      <c r="A433" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B433" s="8" t="s">
+      <c r="B433" s="14" t="s">
         <v>915</v>
       </c>
-      <c r="C433" s="8" t="s">
+      <c r="C433" s="14" t="s">
         <v>916</v>
       </c>
-      <c r="D433" s="11" t="s">
+      <c r="D433" s="17" t="s">
         <v>917</v>
       </c>
     </row>
     <row r="434" spans="1:4">
-      <c r="A434" s="8" t="s">
+      <c r="A434" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B434" s="8" t="s">
+      <c r="B434" s="14" t="s">
         <v>915</v>
       </c>
-      <c r="C434" s="8" t="s">
+      <c r="C434" s="14" t="s">
         <v>918</v>
       </c>
-      <c r="D434" s="11" t="s">
+      <c r="D434" s="17" t="s">
         <v>919</v>
       </c>
     </row>
     <row r="435" spans="1:4">
-      <c r="A435" s="8" t="s">
+      <c r="A435" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B435" s="8" t="s">
+      <c r="B435" s="14" t="s">
         <v>915</v>
       </c>
-      <c r="C435" s="8" t="s">
+      <c r="C435" s="14" t="s">
         <v>920</v>
       </c>
-      <c r="D435" s="11" t="s">
+      <c r="D435" s="17" t="s">
         <v>921</v>
       </c>
     </row>
     <row r="436" spans="1:4">
-      <c r="A436" s="8" t="s">
+      <c r="A436" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B436" s="8" t="s">
+      <c r="B436" s="14" t="s">
         <v>915</v>
       </c>
-      <c r="C436" s="8" t="s">
+      <c r="C436" s="14" t="s">
         <v>922</v>
       </c>
-      <c r="D436" s="11" t="s">
+      <c r="D436" s="17" t="s">
         <v>923</v>
       </c>
     </row>
     <row r="437" spans="1:4">
-      <c r="A437" s="8" t="s">
+      <c r="A437" s="14" t="s">
         <v>905</v>
       </c>
-      <c r="B437" s="8" t="s">
+      <c r="B437" s="14" t="s">
         <v>915</v>
       </c>
-      <c r="C437" s="8" t="s">
+      <c r="C437" s="14" t="s">
         <v>924</v>
       </c>
-      <c r="D437" s="11" t="s">
+      <c r="D437" s="17" t="s">
         <v>925</v>
       </c>
     </row>
     <row r="438" spans="1:4">
-      <c r="A438" s="8" t="s">
+      <c r="A438" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B438" s="8" t="s">
+      <c r="B438" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C438" s="8" t="s">
+      <c r="C438" s="14" t="s">
         <v>928</v>
       </c>
     </row>
     <row r="439" spans="1:4">
-      <c r="A439" s="8" t="s">
+      <c r="A439" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B439" s="8" t="s">
+      <c r="B439" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C439" s="8" t="s">
+      <c r="C439" s="14" t="s">
         <v>929</v>
       </c>
     </row>
     <row r="440" spans="1:4">
-      <c r="A440" s="8" t="s">
+      <c r="A440" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B440" s="8" t="s">
+      <c r="B440" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C440" s="8" t="s">
+      <c r="C440" s="14" t="s">
         <v>930</v>
       </c>
     </row>
     <row r="441" spans="1:4">
-      <c r="A441" s="8" t="s">
+      <c r="A441" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B441" s="8" t="s">
+      <c r="B441" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C441" s="8" t="s">
+      <c r="C441" s="14" t="s">
         <v>931</v>
       </c>
     </row>
     <row r="442" spans="1:4">
-      <c r="A442" s="8" t="s">
+      <c r="A442" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B442" s="8" t="s">
+      <c r="B442" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C442" s="8" t="s">
+      <c r="C442" s="14" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="443" spans="1:4">
-      <c r="A443" s="8" t="s">
+      <c r="A443" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B443" s="8" t="s">
+      <c r="B443" s="14" t="s">
         <v>927</v>
       </c>
-      <c r="C443" s="8" t="s">
+      <c r="C443" s="14" t="s">
         <v>933</v>
       </c>
     </row>
     <row r="444" spans="1:4">
-      <c r="A444" s="8" t="s">
+      <c r="A444" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B444" s="8" t="s">
+      <c r="B444" s="14" t="s">
         <v>934</v>
       </c>
-      <c r="C444" s="8" t="s">
+      <c r="C444" s="14" t="s">
         <v>935</v>
       </c>
     </row>
     <row r="445" spans="1:4">
-      <c r="A445" s="8" t="s">
+      <c r="A445" s="14" t="s">
         <v>926</v>
       </c>
-      <c r="B445" s="8" t="s">
+      <c r="B445" s="14" t="s">
         <v>934</v>
       </c>
-      <c r="C445" s="8" t="s">
+      <c r="C445" s="14" t="s">
         <v>936</v>
       </c>
     </row>
     <row r="446" spans="1:4">
-      <c r="A446" s="8" t="s">
+      <c r="A446" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B446" s="8" t="s">
+      <c r="B446" s="14" t="s">
         <v>938</v>
       </c>
-      <c r="C446" s="8" t="s">
+      <c r="C446" s="14" t="s">
         <v>939</v>
       </c>
     </row>
     <row r="447" spans="1:4">
-      <c r="A447" s="8" t="s">
+      <c r="A447" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B447" s="8" t="s">
+      <c r="B447" s="14" t="s">
         <v>938</v>
       </c>
-      <c r="C447" s="8" t="s">
+      <c r="C447" s="14" t="s">
         <v>940</v>
       </c>
     </row>
     <row r="448" spans="1:4">
-      <c r="A448" s="8" t="s">
+      <c r="A448" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B448" s="8" t="s">
+      <c r="B448" s="14" t="s">
         <v>941</v>
       </c>
-      <c r="C448" s="8" t="s">
+      <c r="C448" s="14" t="s">
         <v>942</v>
       </c>
     </row>
     <row r="449" spans="1:3">
-      <c r="A449" s="8" t="s">
+      <c r="A449" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B449" s="8" t="s">
+      <c r="B449" s="14" t="s">
         <v>941</v>
       </c>
-      <c r="C449" s="8" t="s">
+      <c r="C449" s="14" t="s">
         <v>943</v>
       </c>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="8" t="s">
+      <c r="A450" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B450" s="8" t="s">
+      <c r="B450" s="14" t="s">
         <v>944</v>
       </c>
-      <c r="C450" s="8" t="s">
+      <c r="C450" s="14" t="s">
         <v>945</v>
       </c>
     </row>
     <row r="451" spans="1:3">
-      <c r="A451" s="8" t="s">
+      <c r="A451" s="14" t="s">
         <v>937</v>
       </c>
-      <c r="B451" s="8" t="s">
+      <c r="B451" s="14" t="s">
         <v>944</v>
       </c>
-      <c r="C451" s="8" t="s">
+      <c r="C451" s="14" t="s">
         <v>946</v>
       </c>
     </row>
     <row r="452" spans="1:3">
-      <c r="A452" s="8" t="s">
+      <c r="A452" s="14" t="s">
         <v>947</v>
       </c>
-      <c r="B452" s="8" t="s">
+      <c r="B452" s="14" t="s">
         <v>948</v>
       </c>
-      <c r="C452" s="8" t="s">
+      <c r="C452" s="14" t="s">
         <v>949</v>
       </c>
     </row>
     <row r="453" spans="1:3">
-      <c r="A453" s="8" t="s">
+      <c r="A453" s="14" t="s">
         <v>947</v>
       </c>
-      <c r="B453" s="8" t="s">
+      <c r="B453" s="14" t="s">
         <v>948</v>
       </c>
-      <c r="C453" s="8" t="s">
+      <c r="C453" s="14" t="s">
         <v>950</v>
       </c>
     </row>
     <row r="454" spans="1:3">
-      <c r="A454" s="8" t="s">
+      <c r="A454" s="14" t="s">
         <v>947</v>
       </c>
-      <c r="B454" s="8" t="s">
+      <c r="B454" s="14" t="s">
         <v>951</v>
       </c>
-      <c r="C454" s="8" t="s">
+      <c r="C454" s="14" t="s">
         <v>952</v>
       </c>
     </row>
     <row r="455" spans="1:3">
-      <c r="A455" s="8" t="s">
+      <c r="A455" s="14" t="s">
         <v>947</v>
       </c>
-      <c r="B455" s="8" t="s">
+      <c r="B455" s="14" t="s">
         <v>951</v>
       </c>
-      <c r="C455" s="8" t="s">
+      <c r="C455" s="14" t="s">
         <v>953</v>
       </c>
     </row>
@@ -10592,57 +10665,66 @@
         <v>983</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" ht="141.75" spans="1:3">
       <c r="A12" s="8" t="s">
         <v>984</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="9" t="s">
         <v>985</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="8" t="s">
+      <c r="C12" s="10" t="s">
         <v>986</v>
       </c>
     </row>
+    <row r="13" ht="76" customHeight="1" spans="1:3">
+      <c r="A13" s="11" t="s">
+        <v>987</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>988</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>989</v>
+      </c>
+    </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="14"/>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="14"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="14"/>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="8"/>
+      <c r="A17" s="14"/>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="8"/>
+      <c r="A18" s="14"/>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="8"/>
+      <c r="A19" s="14"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="8"/>
+      <c r="A20" s="14"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="8"/>
+      <c r="A21" s="14"/>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="8"/>
+      <c r="A22" s="14"/>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="8"/>
+      <c r="A23" s="14"/>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="8"/>
+      <c r="A24" s="14"/>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="8"/>
+      <c r="A25" s="14"/>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="8"/>
+      <c r="A26" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
